--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="45">
   <si>
     <t>Дата</t>
   </si>
@@ -53,18 +53,6 @@
   </si>
   <si>
     <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>2026-05-14</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
   </si>
   <si>
     <t>B6386HH</t>
@@ -167,8 +155,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -254,11 +243,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -266,9 +256,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -563,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -622,20 +612,20 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
+      <c r="A2" s="2">
+        <v>46150</v>
       </c>
       <c r="B2">
         <v>1147</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F2">
         <v>61.307</v>
@@ -653,7 +643,7 @@
         <v>109.74</v>
       </c>
       <c r="K2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -663,20 +653,20 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>14</v>
+      <c r="A3" s="2">
+        <v>46153</v>
       </c>
       <c r="B3">
         <v>1199</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F3">
         <v>74</v>
@@ -694,7 +684,7 @@
         <v>132.46</v>
       </c>
       <c r="K3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -704,20 +694,20 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>14</v>
+      <c r="A4" s="2">
+        <v>46153</v>
       </c>
       <c r="B4">
         <v>1199</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F4">
         <v>43</v>
@@ -735,7 +725,7 @@
         <v>76.97</v>
       </c>
       <c r="K4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -745,20 +735,20 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>14</v>
+      <c r="A5" s="2">
+        <v>46153</v>
       </c>
       <c r="B5">
         <v>1911</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
         <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>31</v>
       </c>
       <c r="F5">
         <v>41.419</v>
@@ -776,7 +766,7 @@
         <v>74.14</v>
       </c>
       <c r="K5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -786,20 +776,20 @@
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>15</v>
+      <c r="A6" s="2">
+        <v>46156</v>
       </c>
       <c r="B6">
         <v>1199</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
         <v>28</v>
-      </c>
-      <c r="E6" t="s">
-        <v>32</v>
       </c>
       <c r="F6">
         <v>56.332</v>
@@ -817,7 +807,7 @@
         <v>113.79</v>
       </c>
       <c r="K6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -827,20 +817,20 @@
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" t="s">
-        <v>16</v>
+      <c r="A7" s="2">
+        <v>46157</v>
       </c>
       <c r="B7">
         <v>1147</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F7">
         <v>54.688</v>
@@ -858,7 +848,7 @@
         <v>96.25</v>
       </c>
       <c r="K7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -868,20 +858,20 @@
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>16</v>
+      <c r="A8" s="2">
+        <v>46157</v>
       </c>
       <c r="B8">
         <v>1199</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F8">
         <v>66.188</v>
@@ -899,7 +889,7 @@
         <v>116.49</v>
       </c>
       <c r="K8" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -908,115 +898,110 @@
         <v>267045</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
-      <c r="F9">
+    <row r="11" spans="1:13">
+      <c r="A11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="6">
+        <v>340.602</v>
+      </c>
+      <c r="C13" s="6">
+        <v>6</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1.7494</v>
+      </c>
+      <c r="E13" s="6">
+        <v>595.84</v>
+      </c>
+      <c r="F13" s="6">
+        <v>606.05</v>
+      </c>
+      <c r="G13" s="6">
+        <v>10.21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="6">
+        <v>56.332</v>
+      </c>
+      <c r="C14" s="6">
+        <v>1</v>
+      </c>
+      <c r="D14" s="6">
+        <v>2.02</v>
+      </c>
+      <c r="E14" s="6">
+        <v>113.79</v>
+      </c>
+      <c r="F14" s="6">
+        <v>113.79</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="8">
         <v>396.934</v>
       </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="5">
-        <v>340.602</v>
-      </c>
-      <c r="C14" s="5">
-        <v>6</v>
-      </c>
-      <c r="D14" s="5">
-        <v>1.7494</v>
-      </c>
-      <c r="E14" s="5">
-        <v>595.84</v>
-      </c>
-      <c r="F14" s="5">
-        <v>606.05</v>
-      </c>
-      <c r="G14" s="5">
-        <v>10.21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="5">
-        <v>56.332</v>
-      </c>
-      <c r="C15" s="5">
-        <v>1</v>
-      </c>
-      <c r="D15" s="5">
-        <v>2.02</v>
-      </c>
-      <c r="E15" s="5">
-        <v>113.79</v>
-      </c>
-      <c r="F15" s="5">
-        <v>113.79</v>
-      </c>
-      <c r="G15" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16" s="7">
-        <v>396.934</v>
-      </c>
-      <c r="C16" s="7">
+      <c r="C15" s="8">
         <v>7</v>
       </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7">
+      <c r="D15" s="8"/>
+      <c r="E15" s="8">
         <v>709.63</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F15" s="8">
         <v>719.84</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G15" s="8">
         <v>10.21</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
@@ -209,7 +209,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -219,12 +219,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -275,17 +269,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="34">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,112 +46,58 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>1148 Варна пристанище</t>
-  </si>
-  <si>
-    <t>1911 O5 Варна</t>
-  </si>
-  <si>
-    <t>1199 Varna Car Osvoboditel</t>
-  </si>
-  <si>
-    <t>1147 Варна Ситроен</t>
+    <t>Варна Варненчик</t>
+  </si>
+  <si>
+    <t>Варна</t>
   </si>
   <si>
     <t>B6386HH</t>
   </si>
   <si>
+    <t>B5379XE</t>
+  </si>
+  <si>
+    <t>B8917BP</t>
+  </si>
+  <si>
+    <t>B5383XE</t>
+  </si>
+  <si>
+    <t>B4161TK</t>
+  </si>
+  <si>
+    <t>B7846TP</t>
+  </si>
+  <si>
     <t>B4160TK</t>
   </si>
   <si>
-    <t>B4161TK</t>
-  </si>
-  <si>
-    <t>B9208BM</t>
-  </si>
-  <si>
-    <t>B0452TC</t>
-  </si>
-  <si>
-    <t>B2207PP</t>
-  </si>
-  <si>
     <t>78970155027721301</t>
   </si>
   <si>
+    <t>78970155027721244</t>
+  </si>
+  <si>
+    <t>78970155027721269</t>
+  </si>
+  <si>
+    <t>78970155027721236</t>
+  </si>
+  <si>
+    <t>78970155027721285</t>
+  </si>
+  <si>
+    <t>78970155027721194</t>
+  </si>
+  <si>
     <t>78970155027721293</t>
   </si>
   <si>
-    <t>78970155027721285</t>
-  </si>
-  <si>
-    <t>78970155027721186</t>
-  </si>
-  <si>
-    <t>78970155027721202</t>
-  </si>
-  <si>
-    <t>78970155027721178</t>
-  </si>
-  <si>
     <t>DIESEL EKONOMY</t>
-  </si>
-  <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>10:32:00</t>
-  </si>
-  <si>
-    <t>13:26:00</t>
-  </si>
-  <si>
-    <t>13:08:00</t>
-  </si>
-  <si>
-    <t>13:53:00</t>
-  </si>
-  <si>
-    <t>12:35:00</t>
-  </si>
-  <si>
-    <t>10:22:00</t>
-  </si>
-  <si>
-    <t>13:50:00</t>
-  </si>
-  <si>
-    <t>3232154886 3232154886</t>
-  </si>
-  <si>
-    <t>3232120290 3232120290</t>
-  </si>
-  <si>
-    <t>3232247940 3232247940</t>
-  </si>
-  <si>
-    <t>3232420058 3232420058</t>
-  </si>
-  <si>
-    <t>3232522365 3232522365</t>
-  </si>
-  <si>
-    <t>3232547247 3232547247</t>
-  </si>
-  <si>
-    <t>3232580418 3232580418</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ</t>
@@ -574,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -583,17 +526,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -627,415 +567,358 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2">
+        <v>66.88</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="H2">
+        <v>111.02</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.69</v>
+      </c>
+      <c r="J2">
+        <v>113.03</v>
+      </c>
+      <c r="K2">
+        <v>75731</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46162</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3">
+        <v>71</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="H3">
+        <v>117.86</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.69</v>
+      </c>
+      <c r="J3">
+        <v>119.99</v>
+      </c>
+      <c r="K3">
+        <v>5550</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46175</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4">
+        <v>30</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="H4">
+        <v>49.8</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.69</v>
+      </c>
+      <c r="J4">
+        <v>50.7</v>
+      </c>
+      <c r="K4">
+        <v>74130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3">
+        <v>46176</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5">
+        <v>63</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="H5">
+        <v>104.58</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.69</v>
+      </c>
+      <c r="J5">
+        <v>106.47</v>
+      </c>
+      <c r="K5">
+        <v>6520</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
         <v>24</v>
       </c>
-      <c r="E2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2">
-        <v>72</v>
-      </c>
-      <c r="G2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2">
-        <v>1.72</v>
-      </c>
-      <c r="I2" s="1">
-        <v>123.84</v>
-      </c>
-      <c r="J2">
-        <v>1.75</v>
-      </c>
-      <c r="K2" s="1">
-        <v>126</v>
-      </c>
-      <c r="L2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46162</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3">
-        <v>41.42</v>
-      </c>
-      <c r="G3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3">
-        <v>1.72</v>
-      </c>
-      <c r="I3" s="1">
-        <v>71.23999999999999</v>
-      </c>
-      <c r="J3">
-        <v>1.75</v>
-      </c>
-      <c r="K3" s="1">
-        <v>72.48</v>
-      </c>
-      <c r="L3" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3">
-        <v>53970</v>
-      </c>
-      <c r="N3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46164</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4">
-        <v>25.91</v>
-      </c>
-      <c r="G4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4">
-        <v>1.71</v>
-      </c>
-      <c r="I4" s="1">
-        <v>44.31</v>
-      </c>
-      <c r="J4">
-        <v>1.74</v>
-      </c>
-      <c r="K4" s="1">
-        <v>45.08</v>
-      </c>
-      <c r="L4" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4">
-        <v>53433</v>
-      </c>
-      <c r="N4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="3">
-        <v>46168</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E6" t="s">
         <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5">
-        <v>20</v>
-      </c>
-      <c r="G5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5">
-        <v>1.69</v>
-      </c>
-      <c r="I5" s="1">
-        <v>33.8</v>
-      </c>
-      <c r="J5">
-        <v>1.72</v>
-      </c>
-      <c r="K5" s="1">
-        <v>34.4</v>
-      </c>
-      <c r="L5" t="s">
-        <v>36</v>
-      </c>
-      <c r="M5">
-        <v>402109</v>
-      </c>
-      <c r="N5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="3">
-        <v>46170</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" t="s">
-        <v>30</v>
       </c>
       <c r="F6">
         <v>50</v>
       </c>
-      <c r="G6" t="s">
-        <v>32</v>
+      <c r="G6" s="1">
+        <v>1.63</v>
       </c>
       <c r="H6">
-        <v>1.68</v>
+        <v>81.5</v>
       </c>
       <c r="I6" s="1">
-        <v>84</v>
+        <v>1.66</v>
       </c>
       <c r="J6">
-        <v>1.71</v>
-      </c>
-      <c r="K6" s="1">
-        <v>85.5</v>
-      </c>
-      <c r="L6" t="s">
-        <v>37</v>
-      </c>
-      <c r="M6">
-        <v>67090</v>
-      </c>
-      <c r="N6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>83</v>
+      </c>
+      <c r="K6">
+        <v>53745</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="3">
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F7">
-        <v>41.58</v>
-      </c>
-      <c r="G7" t="s">
-        <v>32</v>
+        <v>65.33</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1.61</v>
       </c>
       <c r="H7">
-        <v>1.54</v>
+        <v>105.18</v>
       </c>
       <c r="I7" s="1">
-        <v>64.03</v>
+        <v>1.64</v>
       </c>
       <c r="J7">
-        <v>1.57</v>
-      </c>
-      <c r="K7" s="1">
-        <v>65.28</v>
-      </c>
-      <c r="L7" t="s">
-        <v>38</v>
-      </c>
-      <c r="M7">
-        <v>153875</v>
-      </c>
-      <c r="N7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>107.14</v>
+      </c>
+      <c r="K7">
+        <v>76329</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="3">
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
         <v>25</v>
       </c>
       <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8">
+        <v>56.75</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="H8">
+        <v>91.37</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.64</v>
+      </c>
+      <c r="J8">
+        <v>93.06999999999999</v>
+      </c>
+      <c r="K8">
+        <v>30798</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="3">
+        <v>46182</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9">
+        <v>49.89</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="H9">
+        <v>80.31999999999999</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1.64</v>
+      </c>
+      <c r="J9">
+        <v>81.81999999999999</v>
+      </c>
+      <c r="K9">
+        <v>54788</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F8">
-        <v>40.77</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="C13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H8">
-        <v>1.67</v>
-      </c>
-      <c r="I8" s="1">
-        <v>68.09</v>
-      </c>
-      <c r="J8">
-        <v>1.7</v>
-      </c>
-      <c r="K8" s="1">
-        <v>69.31</v>
-      </c>
-      <c r="L8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M8">
-        <v>54363</v>
-      </c>
-      <c r="N8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" s="5" t="s">
+      <c r="E13" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="7">
+        <v>452.85</v>
+      </c>
+      <c r="C14" s="7">
         <v>8</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="7">
-        <v>250.1</v>
-      </c>
-      <c r="C13" s="7">
-        <v>6</v>
-      </c>
-      <c r="D13" s="8">
-        <v>1.7004</v>
-      </c>
-      <c r="E13" s="7">
-        <v>425.28</v>
-      </c>
-      <c r="F13" s="7">
-        <v>432.77</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="7">
-        <v>41.58</v>
-      </c>
-      <c r="C14" s="7">
-        <v>1</v>
-      </c>
       <c r="D14" s="8">
-        <v>1.5399</v>
+        <v>1.6377</v>
       </c>
       <c r="E14" s="7">
-        <v>64.03</v>
+        <v>741.63</v>
       </c>
       <c r="F14" s="7">
-        <v>65.28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>755.22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="9" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="B15" s="10">
-        <v>291.68</v>
+        <v>452.85</v>
       </c>
       <c r="C15" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="10">
-        <v>489.31</v>
+        <v>741.63</v>
       </c>
       <c r="F15" s="10">
-        <v>498.05</v>
+        <v>755.22</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="44">
   <si>
     <t>Дата</t>
   </si>
@@ -46,13 +46,22 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Варненчик</t>
   </si>
   <si>
-    <t>Варна</t>
+    <t>Варна Цар Освободител</t>
+  </si>
+  <si>
+    <t>Варна Евkсиноград</t>
   </si>
   <si>
     <t>B6386HH</t>
@@ -98,6 +107,27 @@
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
+  </si>
+  <si>
+    <t>09:59</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>12:19</t>
+  </si>
+  <si>
+    <t>13:32</t>
+  </si>
+  <si>
+    <t>12:41</t>
+  </si>
+  <si>
+    <t>09:04</t>
+  </si>
+  <si>
+    <t>12:48</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ</t>
@@ -517,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -530,10 +560,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -567,22 +599,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46174</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F2">
         <v>66.88</v>
@@ -599,25 +637,31 @@
       <c r="J2">
         <v>113.03</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2">
         <v>75731</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="M2">
+        <v>111594</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46174</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <v>71</v>
@@ -634,25 +678,31 @@
       <c r="J3">
         <v>119.99</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3">
         <v>5550</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="M3">
+        <v>271567</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46175</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F4">
         <v>30</v>
@@ -669,25 +719,31 @@
       <c r="J4">
         <v>50.7</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4">
         <v>74130</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="M4">
+        <v>271839</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46176</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F5">
         <v>63</v>
@@ -704,25 +760,31 @@
       <c r="J5">
         <v>106.47</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L5">
         <v>6520</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="M5">
+        <v>192314</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46177</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F6">
         <v>50</v>
@@ -739,25 +801,31 @@
       <c r="J6">
         <v>83</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6">
         <v>53745</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="M6">
+        <v>272446</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
         <v>46182</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F7">
         <v>65.33</v>
@@ -774,25 +842,31 @@
       <c r="J7">
         <v>107.14</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7">
         <v>76329</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="M7">
+        <v>195660</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="3">
         <v>46182</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F8">
         <v>56.75</v>
@@ -809,25 +883,31 @@
       <c r="J8">
         <v>93.06999999999999</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8">
         <v>30798</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="M8">
+        <v>195885</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="3">
         <v>46182</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F9">
         <v>49.89</v>
@@ -844,13 +924,19 @@
       <c r="J9">
         <v>81.81999999999999</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L9">
         <v>54788</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="M9">
+        <v>193657</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="4" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -858,18 +944,18 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:13">
       <c r="A13" s="5" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>7</v>
@@ -878,9 +964,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:13">
       <c r="A14" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B14" s="7">
         <v>452.85</v>
@@ -898,9 +984,9 @@
         <v>755.22</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:13">
       <c r="A15" s="9" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B15" s="10">
         <v>452.85</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="48">
   <si>
     <t>Дата</t>
   </si>
@@ -49,85 +49,97 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>Варна</t>
+  </si>
+  <si>
+    <t>Варна Сливница</t>
   </si>
   <si>
     <t>Варна Варненчик</t>
   </si>
   <si>
-    <t>Варна Цар Освободител</t>
-  </si>
-  <si>
-    <t>Варна Евkсиноград</t>
-  </si>
-  <si>
     <t>B6386HH</t>
   </si>
   <si>
+    <t>B8917BP</t>
+  </si>
+  <si>
+    <t>B7845TP</t>
+  </si>
+  <si>
+    <t>B4161TK</t>
+  </si>
+  <si>
+    <t>B4160TK</t>
+  </si>
+  <si>
     <t>B5379XE</t>
   </si>
   <si>
-    <t>B8917BP</t>
-  </si>
-  <si>
-    <t>B5383XE</t>
-  </si>
-  <si>
-    <t>B4161TK</t>
-  </si>
-  <si>
-    <t>B7846TP</t>
-  </si>
-  <si>
-    <t>B4160TK</t>
+    <t>B2207PP</t>
   </si>
   <si>
     <t>78970155027721301</t>
   </si>
   <si>
+    <t>78970155027721269</t>
+  </si>
+  <si>
+    <t>78970155027721251</t>
+  </si>
+  <si>
+    <t>78970155027721285</t>
+  </si>
+  <si>
+    <t>78970155027721293</t>
+  </si>
+  <si>
     <t>78970155027721244</t>
   </si>
   <si>
-    <t>78970155027721269</t>
-  </si>
-  <si>
-    <t>78970155027721236</t>
-  </si>
-  <si>
-    <t>78970155027721285</t>
-  </si>
-  <si>
-    <t>78970155027721194</t>
-  </si>
-  <si>
-    <t>78970155027721293</t>
+    <t>78970155027721178</t>
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>09:59</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>12:19</t>
-  </si>
-  <si>
-    <t>13:32</t>
-  </si>
-  <si>
-    <t>12:41</t>
-  </si>
-  <si>
-    <t>09:04</t>
-  </si>
-  <si>
-    <t>12:48</t>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>2026-06-16 10:22:03</t>
+  </si>
+  <si>
+    <t>2026-06-16 12:49:25</t>
+  </si>
+  <si>
+    <t>2026-06-16 13:55:46</t>
+  </si>
+  <si>
+    <t>2026-06-17 09:58:04</t>
+  </si>
+  <si>
+    <t>2026-06-17 13:47:47</t>
+  </si>
+  <si>
+    <t>2026-06-18 12:27:29</t>
+  </si>
+  <si>
+    <t>2026-06-22 10:14:50</t>
+  </si>
+  <si>
+    <t>2026-06-24 10:51:10</t>
+  </si>
+  <si>
+    <t>2026-06-24 10:52:52</t>
+  </si>
+  <si>
+    <t>2026-06-24 13:01:35</t>
+  </si>
+  <si>
+    <t>2026-06-24 13:27:51</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ</t>
@@ -547,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -560,12 +572,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -599,224 +609,188 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46189</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3">
-        <v>46174</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F2">
-        <v>66.88</v>
+        <v>63</v>
       </c>
       <c r="G2" s="1">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="H2">
-        <v>111.02</v>
+        <v>98.28</v>
       </c>
       <c r="I2" s="1">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="J2">
-        <v>113.03</v>
+        <v>100.17</v>
       </c>
       <c r="K2" t="s">
         <v>31</v>
       </c>
-      <c r="L2">
-        <v>75731</v>
-      </c>
-      <c r="M2">
-        <v>111594</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="3">
-        <v>46174</v>
+        <v>46189</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3">
-        <v>71</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="G3" s="1">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="H3">
-        <v>117.86</v>
+        <v>109.26</v>
       </c>
       <c r="I3" s="1">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="J3">
-        <v>119.99</v>
+        <v>111.36</v>
       </c>
       <c r="K3" t="s">
         <v>32</v>
       </c>
-      <c r="L3">
-        <v>5550</v>
-      </c>
-      <c r="M3">
-        <v>271567</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="3">
-        <v>46175</v>
+        <v>46189</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G4" s="1">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="H4">
-        <v>49.8</v>
+        <v>78</v>
       </c>
       <c r="I4" s="1">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="J4">
-        <v>50.7</v>
+        <v>79.5</v>
       </c>
       <c r="K4" t="s">
         <v>33</v>
       </c>
-      <c r="L4">
-        <v>74130</v>
-      </c>
-      <c r="M4">
-        <v>271839</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="3">
-        <v>46176</v>
+        <v>46190</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F5">
-        <v>63</v>
+        <v>54.53</v>
       </c>
       <c r="G5" s="1">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="H5">
-        <v>104.58</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="I5" s="1">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="J5">
-        <v>106.47</v>
+        <v>86.7</v>
       </c>
       <c r="K5" t="s">
         <v>34</v>
       </c>
-      <c r="L5">
-        <v>6520</v>
-      </c>
-      <c r="M5">
-        <v>192314</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="3">
-        <v>46177</v>
+        <v>46190</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6">
-        <v>50</v>
+        <v>44.48</v>
       </c>
       <c r="G6" s="1">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="H6">
-        <v>81.5</v>
+        <v>69.39</v>
       </c>
       <c r="I6" s="1">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="J6">
-        <v>83</v>
+        <v>70.72</v>
       </c>
       <c r="K6" t="s">
         <v>35</v>
       </c>
-      <c r="L6">
-        <v>53745</v>
-      </c>
-      <c r="M6">
-        <v>272446</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="3">
-        <v>46182</v>
+        <v>46191</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
@@ -825,186 +799,293 @@
         <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>65.33</v>
+        <v>25</v>
       </c>
       <c r="G7" s="1">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="H7">
-        <v>105.18</v>
+        <v>38.75</v>
       </c>
       <c r="I7" s="1">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="J7">
-        <v>107.14</v>
+        <v>39.5</v>
       </c>
       <c r="K7" t="s">
         <v>36</v>
       </c>
-      <c r="L7">
-        <v>76329</v>
-      </c>
-      <c r="M7">
-        <v>195660</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="3">
-        <v>46182</v>
+        <v>46195</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
       <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8">
+        <v>70.06</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="H8">
+        <v>104.39</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J8">
+        <v>106.49</v>
+      </c>
+      <c r="K8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9">
+        <v>70.01000000000001</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H9">
+        <v>103.61</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J9">
+        <v>105.72</v>
+      </c>
+      <c r="K9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
         <v>21</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D10" t="s">
         <v>28</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E10" t="s">
         <v>30</v>
       </c>
-      <c r="F8">
-        <v>56.75</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="H8">
-        <v>91.37</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1.64</v>
-      </c>
-      <c r="J8">
-        <v>93.06999999999999</v>
-      </c>
-      <c r="K8" t="s">
-        <v>35</v>
-      </c>
-      <c r="L8">
-        <v>30798</v>
-      </c>
-      <c r="M8">
-        <v>195885</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="3">
-        <v>46182</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="F10">
+        <v>49.76</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H10">
+        <v>73.64</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J10">
+        <v>75.14</v>
+      </c>
+      <c r="K10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
         <v>29</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F11">
+        <v>36.82</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H11">
+        <v>54.49</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J11">
+        <v>55.6</v>
+      </c>
+      <c r="K11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12">
+        <v>19.01</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H12">
+        <v>28.13</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J12">
+        <v>28.71</v>
+      </c>
+      <c r="K12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="7">
+        <v>502.95</v>
+      </c>
+      <c r="C17" s="7">
+        <v>10</v>
+      </c>
+      <c r="D17" s="8">
+        <v>1.5297</v>
+      </c>
+      <c r="E17" s="7">
+        <v>769.37</v>
+      </c>
+      <c r="F17" s="7">
+        <v>784.47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F9">
-        <v>49.89</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="H9">
-        <v>80.31999999999999</v>
-      </c>
-      <c r="I9" s="1">
-        <v>1.64</v>
-      </c>
-      <c r="J9">
-        <v>81.81999999999999</v>
-      </c>
-      <c r="K9" t="s">
-        <v>37</v>
-      </c>
-      <c r="L9">
-        <v>54788</v>
-      </c>
-      <c r="M9">
-        <v>193657</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="7">
-        <v>452.85</v>
-      </c>
-      <c r="C14" s="7">
-        <v>8</v>
-      </c>
-      <c r="D14" s="8">
-        <v>1.6377</v>
-      </c>
-      <c r="E14" s="7">
-        <v>741.63</v>
-      </c>
-      <c r="F14" s="7">
-        <v>755.22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="10">
-        <v>452.85</v>
-      </c>
-      <c r="C15" s="10">
-        <v>8</v>
-      </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="10">
-        <v>741.63</v>
-      </c>
-      <c r="F15" s="10">
-        <v>755.22</v>
+      <c r="B18" s="7">
+        <v>49.76</v>
+      </c>
+      <c r="C18" s="7">
+        <v>1</v>
+      </c>
+      <c r="D18" s="8">
+        <v>1.4799</v>
+      </c>
+      <c r="E18" s="7">
+        <v>73.64</v>
+      </c>
+      <c r="F18" s="7">
+        <v>75.14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="10">
+        <v>552.71</v>
+      </c>
+      <c r="C19" s="10">
+        <v>11</v>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="E19" s="10">
+        <v>843.01</v>
+      </c>
+      <c r="F19" s="10">
+        <v>859.61</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="72">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,16 +52,25 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>Варна Варненчик</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
   </si>
   <si>
     <t>B6386HH</t>
@@ -82,6 +94,9 @@
     <t>B2207PP</t>
   </si>
   <si>
+    <t>B5383XE</t>
+  </si>
+  <si>
     <t>78970155027721301</t>
   </si>
   <si>
@@ -103,43 +118,100 @@
     <t>78970155027721178</t>
   </si>
   <si>
+    <t>78970155027721236</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-06-16 10:22:03</t>
-  </si>
-  <si>
-    <t>2026-06-16 12:49:25</t>
-  </si>
-  <si>
-    <t>2026-06-16 13:55:46</t>
-  </si>
-  <si>
-    <t>2026-06-17 09:58:04</t>
-  </si>
-  <si>
-    <t>2026-06-17 13:47:47</t>
-  </si>
-  <si>
-    <t>2026-06-18 12:27:29</t>
-  </si>
-  <si>
-    <t>2026-06-22 10:14:50</t>
-  </si>
-  <si>
-    <t>2026-06-24 10:51:10</t>
-  </si>
-  <si>
-    <t>2026-06-24 10:52:52</t>
-  </si>
-  <si>
-    <t>2026-06-24 13:01:35</t>
-  </si>
-  <si>
-    <t>2026-06-24 13:27:51</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>10:22:00</t>
+  </si>
+  <si>
+    <t>12:49:00</t>
+  </si>
+  <si>
+    <t>13:55:00</t>
+  </si>
+  <si>
+    <t>09:58:00</t>
+  </si>
+  <si>
+    <t>13:47:00</t>
+  </si>
+  <si>
+    <t>12:27:00</t>
+  </si>
+  <si>
+    <t>10:14:00</t>
+  </si>
+  <si>
+    <t>10:51:00</t>
+  </si>
+  <si>
+    <t>10:52:00</t>
+  </si>
+  <si>
+    <t>13:27:00</t>
+  </si>
+  <si>
+    <t>13:01:00</t>
+  </si>
+  <si>
+    <t>12:55:00</t>
+  </si>
+  <si>
+    <t>11:05:00</t>
+  </si>
+  <si>
+    <t>12:02:00</t>
+  </si>
+  <si>
+    <t>3233433883 3233433883</t>
+  </si>
+  <si>
+    <t>3233444888 3233444888</t>
+  </si>
+  <si>
+    <t>3233447208 3233447208</t>
+  </si>
+  <si>
+    <t>3233472278 3233472278</t>
+  </si>
+  <si>
+    <t>3233479601 3233479601</t>
+  </si>
+  <si>
+    <t>3233524788 3233524788</t>
+  </si>
+  <si>
+    <t>3233710347 3233710347</t>
+  </si>
+  <si>
+    <t>3233800481 3233800481</t>
+  </si>
+  <si>
+    <t>3233819349 3233819349</t>
+  </si>
+  <si>
+    <t>3233820737 3233820737</t>
+  </si>
+  <si>
+    <t>3233806909 3233806909</t>
+  </si>
+  <si>
+    <t>3234094788 3234094788</t>
+  </si>
+  <si>
+    <t>3234110039 3234110039</t>
+  </si>
+  <si>
+    <t>3234095852 3234095852</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ</t>
@@ -559,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -568,14 +640,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -609,483 +684,723 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F2">
         <v>63</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2">
         <v>1.56</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>98.28</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.59</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>100.17</v>
       </c>
-      <c r="K2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2">
+        <v>76850</v>
+      </c>
+      <c r="N2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46189</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F3">
         <v>70.04000000000001</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3">
         <v>1.56</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>109.26</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.59</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>111.36</v>
       </c>
-      <c r="K3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3">
+        <v>74426</v>
+      </c>
+      <c r="N3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46189</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F4">
         <v>50</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4">
         <v>1.56</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>78</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.59</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>79.5</v>
       </c>
-      <c r="K4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M4">
+        <v>38170</v>
+      </c>
+      <c r="N4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46190</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F5">
         <v>54.53</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5">
         <v>1.56</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>85.06999999999999</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.59</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>86.7</v>
       </c>
-      <c r="K5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5">
+        <v>54161</v>
+      </c>
+      <c r="N5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46190</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F6">
         <v>44.48</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6">
         <v>1.56</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>69.39</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.59</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>70.72</v>
       </c>
-      <c r="K6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M6">
+        <v>55160</v>
+      </c>
+      <c r="N6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46191</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F7">
         <v>25</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7">
         <v>1.55</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>38.75</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.58</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>39.5</v>
       </c>
-      <c r="K7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7">
+        <v>67720</v>
+      </c>
+      <c r="N7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46195</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F8">
         <v>70.06</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8">
         <v>1.49</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>104.39</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.52</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>106.49</v>
       </c>
-      <c r="K8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M8">
+        <v>6190</v>
+      </c>
+      <c r="N8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>46197</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F9">
         <v>70.01000000000001</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9">
         <v>1.48</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>103.61</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.51</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>105.72</v>
       </c>
-      <c r="K9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9" t="s">
+        <v>45</v>
+      </c>
+      <c r="M9">
+        <v>77450</v>
+      </c>
+      <c r="N9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>46197</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F10">
         <v>49.76</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10">
         <v>1.48</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>73.64</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.51</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>75.14</v>
       </c>
-      <c r="K10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10" t="s">
+        <v>46</v>
+      </c>
+      <c r="M10">
+        <v>154202</v>
+      </c>
+      <c r="N10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
         <v>46197</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F11">
-        <v>36.82</v>
-      </c>
-      <c r="G11" s="1">
+        <v>19.01</v>
+      </c>
+      <c r="G11" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11">
         <v>1.48</v>
       </c>
-      <c r="H11">
-        <v>54.49</v>
-      </c>
       <c r="I11" s="1">
+        <v>28.13</v>
+      </c>
+      <c r="J11">
         <v>1.51</v>
       </c>
-      <c r="J11">
-        <v>55.6</v>
-      </c>
-      <c r="K11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="K11" s="1">
+        <v>28.71</v>
+      </c>
+      <c r="L11" t="s">
+        <v>47</v>
+      </c>
+      <c r="M11">
+        <v>544500</v>
+      </c>
+      <c r="N11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
         <v>46197</v>
       </c>
       <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12">
+        <v>36.82</v>
+      </c>
+      <c r="G12" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12">
+        <v>1.48</v>
+      </c>
+      <c r="I12" s="1">
+        <v>54.49</v>
+      </c>
+      <c r="J12">
+        <v>1.51</v>
+      </c>
+      <c r="K12" s="1">
+        <v>55.6</v>
+      </c>
+      <c r="L12" t="s">
+        <v>48</v>
+      </c>
+      <c r="M12">
+        <v>55450</v>
+      </c>
+      <c r="N12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13">
+        <v>72.08</v>
+      </c>
+      <c r="G13" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13">
+        <v>1.48</v>
+      </c>
+      <c r="I13" s="1">
+        <v>106.68</v>
+      </c>
+      <c r="J13">
+        <v>1.51</v>
+      </c>
+      <c r="K13" s="1">
+        <v>108.84</v>
+      </c>
+      <c r="L13" t="s">
+        <v>49</v>
+      </c>
+      <c r="M13">
+        <v>6996</v>
+      </c>
+      <c r="N13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14">
+        <v>19.2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14">
+        <v>1.47</v>
+      </c>
+      <c r="I14" s="1">
+        <v>28.22</v>
+      </c>
+      <c r="J14">
+        <v>1.5</v>
+      </c>
+      <c r="K14" s="1">
+        <v>28.8</v>
+      </c>
+      <c r="L14" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14">
+        <v>1543333336</v>
+      </c>
+      <c r="N14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15">
+        <v>30.72</v>
+      </c>
+      <c r="G15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15">
+        <v>1.48</v>
+      </c>
+      <c r="I15" s="1">
+        <v>45.47</v>
+      </c>
+      <c r="J15">
+        <v>1.51</v>
+      </c>
+      <c r="K15" s="1">
+        <v>46.39</v>
+      </c>
+      <c r="L15" t="s">
+        <v>51</v>
+      </c>
+      <c r="M15">
+        <v>55695</v>
+      </c>
+      <c r="N15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="7">
+        <v>605.75</v>
+      </c>
+      <c r="C20" s="7">
         <v>12</v>
       </c>
-      <c r="C12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F12">
-        <v>19.01</v>
-      </c>
-      <c r="G12" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="H12">
-        <v>28.13</v>
-      </c>
-      <c r="I12" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J12">
-        <v>28.71</v>
-      </c>
-      <c r="K12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="7">
-        <v>502.95</v>
-      </c>
-      <c r="C17" s="7">
-        <v>10</v>
-      </c>
-      <c r="D17" s="8">
-        <v>1.5297</v>
-      </c>
-      <c r="E17" s="7">
-        <v>769.37</v>
-      </c>
-      <c r="F17" s="7">
-        <v>784.47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="7">
-        <v>49.76</v>
-      </c>
-      <c r="C18" s="7">
-        <v>1</v>
-      </c>
-      <c r="D18" s="8">
-        <v>1.4799</v>
-      </c>
-      <c r="E18" s="7">
-        <v>73.64</v>
-      </c>
-      <c r="F18" s="7">
-        <v>75.14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="10">
-        <v>552.71</v>
-      </c>
-      <c r="C19" s="10">
-        <v>11</v>
-      </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="10">
-        <v>843.01</v>
-      </c>
-      <c r="F19" s="10">
-        <v>859.61</v>
+      <c r="D20" s="8">
+        <v>1.5213</v>
+      </c>
+      <c r="E20" s="7">
+        <v>921.52</v>
+      </c>
+      <c r="F20" s="7">
+        <v>939.7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="7">
+        <v>68.95999999999999</v>
+      </c>
+      <c r="C21" s="7">
+        <v>2</v>
+      </c>
+      <c r="D21" s="8">
+        <v>1.4771</v>
+      </c>
+      <c r="E21" s="7">
+        <v>101.86</v>
+      </c>
+      <c r="F21" s="7">
+        <v>103.94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="10">
+        <v>674.71</v>
+      </c>
+      <c r="C22" s="10">
+        <v>14</v>
+      </c>
+      <c r="D22" s="8"/>
+      <c r="E22" s="10">
+        <v>1023.38</v>
+      </c>
+      <c r="F22" s="10">
+        <v>1043.64</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="55">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,19 +55,16 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1148 Варна пристанище</t>
-  </si>
-  <si>
-    <t>1199 Varna Car Osvoboditel</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>1911 O5 Варна</t>
-  </si>
-  <si>
-    <t>1147 Варна Ситроен</t>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>Варна</t>
+  </si>
+  <si>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>Варна Варненчик</t>
   </si>
   <si>
     <t>B6386HH</t>
@@ -127,91 +121,46 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>10:22:00</t>
-  </si>
-  <si>
-    <t>12:49:00</t>
-  </si>
-  <si>
-    <t>13:55:00</t>
-  </si>
-  <si>
-    <t>09:58:00</t>
-  </si>
-  <si>
-    <t>13:47:00</t>
-  </si>
-  <si>
-    <t>12:27:00</t>
-  </si>
-  <si>
-    <t>10:14:00</t>
-  </si>
-  <si>
-    <t>10:51:00</t>
-  </si>
-  <si>
-    <t>10:52:00</t>
-  </si>
-  <si>
-    <t>13:27:00</t>
-  </si>
-  <si>
-    <t>13:01:00</t>
-  </si>
-  <si>
-    <t>12:55:00</t>
-  </si>
-  <si>
-    <t>11:05:00</t>
-  </si>
-  <si>
-    <t>12:02:00</t>
-  </si>
-  <si>
-    <t>3233433883 3233433883</t>
-  </si>
-  <si>
-    <t>3233444888 3233444888</t>
-  </si>
-  <si>
-    <t>3233447208 3233447208</t>
-  </si>
-  <si>
-    <t>3233472278 3233472278</t>
-  </si>
-  <si>
-    <t>3233479601 3233479601</t>
-  </si>
-  <si>
-    <t>3233524788 3233524788</t>
-  </si>
-  <si>
-    <t>3233710347 3233710347</t>
-  </si>
-  <si>
-    <t>3233800481 3233800481</t>
-  </si>
-  <si>
-    <t>3233819349 3233819349</t>
-  </si>
-  <si>
-    <t>3233820737 3233820737</t>
-  </si>
-  <si>
-    <t>3233806909 3233806909</t>
-  </si>
-  <si>
-    <t>3234094788 3234094788</t>
-  </si>
-  <si>
-    <t>3234110039 3234110039</t>
-  </si>
-  <si>
-    <t>3234095852 3234095852</t>
+    <t>10:22</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>13:56</t>
+  </si>
+  <si>
+    <t>09:58</t>
+  </si>
+  <si>
+    <t>13:47</t>
+  </si>
+  <si>
+    <t>12:27</t>
+  </si>
+  <si>
+    <t>10:14</t>
+  </si>
+  <si>
+    <t>10:52</t>
+  </si>
+  <si>
+    <t>10:53</t>
+  </si>
+  <si>
+    <t>13:01</t>
+  </si>
+  <si>
+    <t>13:28</t>
+  </si>
+  <si>
+    <t>11:07</t>
+  </si>
+  <si>
+    <t>12:03</t>
+  </si>
+  <si>
+    <t>12:56</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ</t>
@@ -631,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -640,17 +589,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -690,629 +638,584 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>63</v>
       </c>
-      <c r="G2" t="s">
-        <v>37</v>
+      <c r="G2" s="1">
+        <v>1.56</v>
       </c>
       <c r="H2">
-        <v>1.56</v>
+        <v>98.28</v>
       </c>
       <c r="I2" s="1">
-        <v>98.28</v>
+        <v>1.59</v>
       </c>
       <c r="J2">
-        <v>1.59</v>
-      </c>
-      <c r="K2" s="1">
         <v>100.17</v>
       </c>
-      <c r="L2" t="s">
-        <v>38</v>
+      <c r="K2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L2">
+        <v>76850</v>
       </c>
       <c r="M2">
-        <v>76850</v>
-      </c>
-      <c r="N2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>219746</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46189</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F3">
         <v>70.04000000000001</v>
       </c>
-      <c r="G3" t="s">
-        <v>37</v>
+      <c r="G3" s="1">
+        <v>1.56</v>
       </c>
       <c r="H3">
-        <v>1.56</v>
+        <v>109.26</v>
       </c>
       <c r="I3" s="1">
-        <v>109.26</v>
+        <v>1.59</v>
       </c>
       <c r="J3">
-        <v>1.59</v>
-      </c>
-      <c r="K3" s="1">
         <v>111.36</v>
       </c>
-      <c r="L3" t="s">
-        <v>39</v>
+      <c r="K3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3">
+        <v>74426</v>
       </c>
       <c r="M3">
-        <v>74426</v>
-      </c>
-      <c r="N3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>275723</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46189</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F4">
         <v>50</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="H4">
+        <v>78</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.59</v>
+      </c>
+      <c r="J4">
+        <v>79.5</v>
+      </c>
+      <c r="K4" t="s">
         <v>37</v>
       </c>
-      <c r="H4">
-        <v>1.56</v>
-      </c>
-      <c r="I4" s="1">
-        <v>78</v>
-      </c>
-      <c r="J4">
-        <v>1.59</v>
-      </c>
-      <c r="K4" s="1">
-        <v>79.5</v>
-      </c>
-      <c r="L4" t="s">
-        <v>40</v>
+      <c r="L4">
+        <v>38170</v>
       </c>
       <c r="M4">
-        <v>38170</v>
-      </c>
-      <c r="N4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>275745</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46190</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F5">
         <v>54.53</v>
       </c>
-      <c r="G5" t="s">
-        <v>37</v>
+      <c r="G5" s="1">
+        <v>1.56</v>
       </c>
       <c r="H5">
-        <v>1.56</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="I5" s="1">
-        <v>85.06999999999999</v>
+        <v>1.59</v>
       </c>
       <c r="J5">
-        <v>1.59</v>
-      </c>
-      <c r="K5" s="1">
         <v>86.7</v>
       </c>
-      <c r="L5" t="s">
-        <v>41</v>
+      <c r="K5" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5">
+        <v>54161</v>
       </c>
       <c r="M5">
-        <v>54161</v>
-      </c>
-      <c r="N5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>142948</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46190</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F6">
         <v>44.48</v>
       </c>
-      <c r="G6" t="s">
-        <v>37</v>
+      <c r="G6" s="1">
+        <v>1.56</v>
       </c>
       <c r="H6">
-        <v>1.56</v>
+        <v>69.39</v>
       </c>
       <c r="I6" s="1">
-        <v>69.39</v>
+        <v>1.59</v>
       </c>
       <c r="J6">
-        <v>1.59</v>
-      </c>
-      <c r="K6" s="1">
         <v>70.72</v>
       </c>
-      <c r="L6" t="s">
-        <v>42</v>
+      <c r="K6" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6">
+        <v>55160</v>
       </c>
       <c r="M6">
-        <v>55160</v>
-      </c>
-      <c r="N6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>198185</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
         <v>46191</v>
       </c>
       <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
         <v>18</v>
       </c>
-      <c r="C7" t="s">
-        <v>20</v>
-      </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F7">
         <v>25</v>
       </c>
-      <c r="G7" t="s">
-        <v>37</v>
+      <c r="G7" s="1">
+        <v>1.55</v>
       </c>
       <c r="H7">
-        <v>1.55</v>
+        <v>38.75</v>
       </c>
       <c r="I7" s="1">
-        <v>38.75</v>
+        <v>1.58</v>
       </c>
       <c r="J7">
-        <v>1.58</v>
-      </c>
-      <c r="K7" s="1">
         <v>39.5</v>
       </c>
-      <c r="L7" t="s">
-        <v>43</v>
+      <c r="K7" t="s">
+        <v>40</v>
+      </c>
+      <c r="L7">
+        <v>67720</v>
       </c>
       <c r="M7">
-        <v>67720</v>
-      </c>
-      <c r="N7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>116276</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="3">
         <v>46195</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F8">
         <v>70.06</v>
       </c>
-      <c r="G8" t="s">
-        <v>37</v>
+      <c r="G8" s="1">
+        <v>1.49</v>
       </c>
       <c r="H8">
-        <v>1.49</v>
+        <v>104.39</v>
       </c>
       <c r="I8" s="1">
-        <v>104.39</v>
+        <v>1.52</v>
       </c>
       <c r="J8">
-        <v>1.52</v>
-      </c>
-      <c r="K8" s="1">
         <v>106.49</v>
       </c>
-      <c r="L8" t="s">
-        <v>44</v>
+      <c r="K8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L8">
+        <v>6190</v>
       </c>
       <c r="M8">
-        <v>6190</v>
-      </c>
-      <c r="N8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>144469</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="3">
         <v>46197</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F9">
         <v>70.01000000000001</v>
       </c>
-      <c r="G9" t="s">
-        <v>37</v>
+      <c r="G9" s="1">
+        <v>1.48</v>
       </c>
       <c r="H9">
-        <v>1.48</v>
+        <v>103.61</v>
       </c>
       <c r="I9" s="1">
-        <v>103.61</v>
+        <v>1.51</v>
       </c>
       <c r="J9">
-        <v>1.51</v>
-      </c>
-      <c r="K9" s="1">
         <v>105.72</v>
       </c>
-      <c r="L9" t="s">
-        <v>45</v>
+      <c r="K9" t="s">
+        <v>42</v>
+      </c>
+      <c r="L9">
+        <v>77450</v>
       </c>
       <c r="M9">
-        <v>77450</v>
-      </c>
-      <c r="N9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>223351</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="3">
         <v>46197</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F10">
         <v>49.76</v>
       </c>
-      <c r="G10" t="s">
-        <v>37</v>
+      <c r="G10" s="1">
+        <v>1.48</v>
       </c>
       <c r="H10">
-        <v>1.48</v>
+        <v>73.64</v>
       </c>
       <c r="I10" s="1">
-        <v>73.64</v>
+        <v>1.51</v>
       </c>
       <c r="J10">
-        <v>1.51</v>
-      </c>
-      <c r="K10" s="1">
         <v>75.14</v>
       </c>
-      <c r="L10" t="s">
-        <v>46</v>
+      <c r="K10" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10">
+        <v>154202</v>
       </c>
       <c r="M10">
-        <v>154202</v>
-      </c>
-      <c r="N10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>277926</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="3">
         <v>46197</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F11">
-        <v>19.01</v>
-      </c>
-      <c r="G11" t="s">
-        <v>37</v>
+        <v>36.82</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1.48</v>
       </c>
       <c r="H11">
-        <v>1.48</v>
+        <v>54.49</v>
       </c>
       <c r="I11" s="1">
-        <v>28.13</v>
+        <v>1.51</v>
       </c>
       <c r="J11">
-        <v>1.51</v>
-      </c>
-      <c r="K11" s="1">
-        <v>28.71</v>
-      </c>
-      <c r="L11" t="s">
-        <v>47</v>
+        <v>55.6</v>
+      </c>
+      <c r="K11" t="s">
+        <v>44</v>
+      </c>
+      <c r="L11">
+        <v>55450</v>
       </c>
       <c r="M11">
-        <v>544500</v>
-      </c>
-      <c r="N11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>202691</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="3">
         <v>46197</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F12">
-        <v>36.82</v>
-      </c>
-      <c r="G12" t="s">
-        <v>37</v>
+        <v>19.01</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1.48</v>
       </c>
       <c r="H12">
-        <v>1.48</v>
+        <v>28.13</v>
       </c>
       <c r="I12" s="1">
-        <v>54.49</v>
+        <v>1.51</v>
       </c>
       <c r="J12">
-        <v>1.51</v>
-      </c>
-      <c r="K12" s="1">
-        <v>55.6</v>
-      </c>
-      <c r="L12" t="s">
-        <v>48</v>
+        <v>28.71</v>
+      </c>
+      <c r="K12" t="s">
+        <v>45</v>
+      </c>
+      <c r="L12">
+        <v>544500</v>
       </c>
       <c r="M12">
-        <v>55450</v>
-      </c>
-      <c r="N12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>277979</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="3">
         <v>46203</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" t="s">
         <v>34</v>
       </c>
-      <c r="E13" t="s">
-        <v>35</v>
-      </c>
       <c r="F13">
-        <v>72.08</v>
-      </c>
-      <c r="G13" t="s">
-        <v>37</v>
+        <v>19.2</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1.47</v>
       </c>
       <c r="H13">
-        <v>1.48</v>
+        <v>28.22</v>
       </c>
       <c r="I13" s="1">
-        <v>106.68</v>
+        <v>1.5</v>
       </c>
       <c r="J13">
-        <v>1.51</v>
-      </c>
-      <c r="K13" s="1">
-        <v>108.84</v>
-      </c>
-      <c r="L13" t="s">
-        <v>49</v>
+        <v>28.8</v>
+      </c>
+      <c r="K13" t="s">
+        <v>46</v>
+      </c>
+      <c r="L13">
+        <v>1543333336</v>
       </c>
       <c r="M13">
-        <v>6996</v>
-      </c>
-      <c r="N13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>279546</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="3">
         <v>46203</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" t="s">
         <v>33</v>
       </c>
-      <c r="E14" t="s">
-        <v>36</v>
-      </c>
       <c r="F14">
-        <v>19.2</v>
-      </c>
-      <c r="G14" t="s">
-        <v>37</v>
+        <v>30.72</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1.48</v>
       </c>
       <c r="H14">
-        <v>1.47</v>
+        <v>45.47</v>
       </c>
       <c r="I14" s="1">
-        <v>28.22</v>
+        <v>1.51</v>
       </c>
       <c r="J14">
-        <v>1.5</v>
-      </c>
-      <c r="K14" s="1">
-        <v>28.8</v>
-      </c>
-      <c r="L14" t="s">
-        <v>50</v>
+        <v>46.39</v>
+      </c>
+      <c r="K14" t="s">
+        <v>47</v>
+      </c>
+      <c r="L14">
+        <v>55695</v>
       </c>
       <c r="M14">
-        <v>1543333336</v>
-      </c>
-      <c r="N14" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>206881</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="3">
         <v>46203</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F15">
-        <v>30.72</v>
-      </c>
-      <c r="G15" t="s">
-        <v>37</v>
+        <v>72.08</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1.48</v>
       </c>
       <c r="H15">
-        <v>1.48</v>
+        <v>106.68</v>
       </c>
       <c r="I15" s="1">
-        <v>45.47</v>
+        <v>1.51</v>
       </c>
       <c r="J15">
-        <v>1.51</v>
-      </c>
-      <c r="K15" s="1">
-        <v>46.39</v>
-      </c>
-      <c r="L15" t="s">
-        <v>51</v>
+        <v>108.84</v>
+      </c>
+      <c r="K15" t="s">
+        <v>48</v>
+      </c>
+      <c r="L15">
+        <v>6996</v>
       </c>
       <c r="M15">
-        <v>55695</v>
-      </c>
-      <c r="N15" t="s">
-        <v>65</v>
+        <v>208206</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="4" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -1322,27 +1225,27 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="5" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B20" s="7">
         <v>605.75</v>
@@ -1362,7 +1265,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B21" s="7">
         <v>68.95999999999999</v>
@@ -1382,7 +1285,7 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="9" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="B22" s="10">
         <v>674.71</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="73">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,13 +55,22 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
   </si>
   <si>
     <t>B7846TP</t>
@@ -67,85 +79,142 @@
     <t>B6386HH</t>
   </si>
   <si>
+    <t>B2207PP</t>
+  </si>
+  <si>
+    <t>B7845TP</t>
+  </si>
+  <si>
+    <t>B8917BP</t>
+  </si>
+  <si>
+    <t>B5379XE</t>
+  </si>
+  <si>
+    <t>B4160TK</t>
+  </si>
+  <si>
+    <t>B4161TK</t>
+  </si>
+  <si>
     <t>B0452TC</t>
   </si>
   <si>
-    <t>B4161TK</t>
-  </si>
-  <si>
-    <t>B7845TP</t>
-  </si>
-  <si>
-    <t>B8917BP</t>
-  </si>
-  <si>
-    <t>B5379XE</t>
-  </si>
-  <si>
-    <t>B4160TK</t>
-  </si>
-  <si>
     <t>78970155027721194</t>
   </si>
   <si>
     <t>78970155027721301</t>
   </si>
   <si>
+    <t>78970155027721178</t>
+  </si>
+  <si>
+    <t>78970155027721251</t>
+  </si>
+  <si>
+    <t>78970155027721269</t>
+  </si>
+  <si>
+    <t>78970155027721244</t>
+  </si>
+  <si>
+    <t>78970155027721293</t>
+  </si>
+  <si>
+    <t>78970155027721285</t>
+  </si>
+  <si>
     <t>78970155027721202</t>
   </si>
   <si>
-    <t>78970155027721285</t>
-  </si>
-  <si>
-    <t>78970155027721251</t>
-  </si>
-  <si>
-    <t>78970155027721269</t>
-  </si>
-  <si>
-    <t>78970155027721244</t>
-  </si>
-  <si>
-    <t>78970155027721293</t>
-  </si>
-  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-07-01 09:55:17</t>
-  </si>
-  <si>
-    <t>2026-07-01 10:37:11</t>
-  </si>
-  <si>
-    <t>2026-07-01 12:47:20</t>
-  </si>
-  <si>
-    <t>2026-07-01 13:13:22</t>
-  </si>
-  <si>
-    <t>2026-07-01 13:46:53</t>
-  </si>
-  <si>
-    <t>2026-07-07 08:40:12</t>
-  </si>
-  <si>
-    <t>2026-07-07 13:46:08</t>
-  </si>
-  <si>
-    <t>2026-07-08 12:57:55</t>
-  </si>
-  <si>
-    <t>2026-07-09 09:57:46</t>
-  </si>
-  <si>
-    <t>2026-07-13 12:47:12</t>
-  </si>
-  <si>
-    <t>2026-07-13 13:21:53</t>
-  </si>
-  <si>
-    <t>2026-07-15 13:27:52</t>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>13:24:00</t>
+  </si>
+  <si>
+    <t>10:25:00</t>
+  </si>
+  <si>
+    <t>11:58:00</t>
+  </si>
+  <si>
+    <t>10:55:00</t>
+  </si>
+  <si>
+    <t>13:48:00</t>
+  </si>
+  <si>
+    <t>13:39:00</t>
+  </si>
+  <si>
+    <t>09:54:00</t>
+  </si>
+  <si>
+    <t>10:53:00</t>
+  </si>
+  <si>
+    <t>12:25:00</t>
+  </si>
+  <si>
+    <t>12:40:00</t>
+  </si>
+  <si>
+    <t>13:35:00</t>
+  </si>
+  <si>
+    <t>10:18:00</t>
+  </si>
+  <si>
+    <t>11:33:00</t>
+  </si>
+  <si>
+    <t>3234885564 3234885564</t>
+  </si>
+  <si>
+    <t>3234886279 3234886279</t>
+  </si>
+  <si>
+    <t>3234936196 3234936196</t>
+  </si>
+  <si>
+    <t>3235074627 3235074627</t>
+  </si>
+  <si>
+    <t>3235140449 3235140449</t>
+  </si>
+  <si>
+    <t>3235200889 3235200889</t>
+  </si>
+  <si>
+    <t>3235184369 3235184369</t>
+  </si>
+  <si>
+    <t>3235220100 3235220100</t>
+  </si>
+  <si>
+    <t>3235206246 3235206246</t>
+  </si>
+  <si>
+    <t>3235251806 3235251806</t>
+  </si>
+  <si>
+    <t>3235432507 3235432507</t>
+  </si>
+  <si>
+    <t>3235527830 3235527830</t>
+  </si>
+  <si>
+    <t>3235584569 3235584569</t>
+  </si>
+  <si>
+    <t>3235629731 3235629731</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ</t>
@@ -565,7 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -574,15 +643,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -619,534 +690,720 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46204</v>
+        <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2">
+        <v>56</v>
+      </c>
+      <c r="G2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2">
+        <v>1.58</v>
+      </c>
+      <c r="I2" s="1">
+        <v>88.48</v>
+      </c>
+      <c r="J2">
+        <v>1.61</v>
+      </c>
+      <c r="K2" s="1">
+        <v>90.16</v>
+      </c>
+      <c r="L2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M2">
+        <v>31596</v>
+      </c>
+      <c r="N2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46219</v>
+      </c>
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="G3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3">
+        <v>1.58</v>
+      </c>
+      <c r="I3" s="1">
+        <v>103.33</v>
+      </c>
+      <c r="J3">
+        <v>1.61</v>
+      </c>
+      <c r="K3" s="1">
+        <v>105.29</v>
+      </c>
+      <c r="L3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3">
+        <v>79080</v>
+      </c>
+      <c r="N3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4">
+        <v>39.17</v>
+      </c>
+      <c r="G4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4">
+        <v>1.48</v>
+      </c>
+      <c r="I4" s="1">
+        <v>57.97</v>
+      </c>
+      <c r="J4">
+        <v>1.51</v>
+      </c>
+      <c r="K4" s="1">
+        <v>59.15</v>
+      </c>
+      <c r="L4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M4">
+        <v>145632</v>
+      </c>
+      <c r="N4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="3">
+        <v>46223</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
         <v>31</v>
       </c>
-      <c r="F2">
-        <v>58</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="H2">
-        <v>85.84</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J2">
-        <v>87.58</v>
-      </c>
-      <c r="K2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2">
-        <v>31218</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="3">
-        <v>46204</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3">
-        <v>62.01</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="H3">
-        <v>91.77</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J3">
-        <v>93.64</v>
-      </c>
-      <c r="K3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3">
-        <v>77960</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="3">
-        <v>46204</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4">
-        <v>30</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="H4">
-        <v>44.4</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J4">
-        <v>45.3</v>
-      </c>
-      <c r="K4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4">
-        <v>67477</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="3">
-        <v>46204</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F5">
-        <v>53.83</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.48</v>
+        <v>51.61</v>
+      </c>
+      <c r="G5" t="s">
+        <v>39</v>
       </c>
       <c r="H5">
-        <v>79.67</v>
+        <v>1.65</v>
       </c>
       <c r="I5" s="1">
-        <v>1.51</v>
+        <v>85.16</v>
       </c>
       <c r="J5">
-        <v>81.28</v>
-      </c>
-      <c r="K5" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5">
-        <v>547001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>1.68</v>
+      </c>
+      <c r="K5" s="1">
+        <v>86.7</v>
+      </c>
+      <c r="L5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5">
+        <v>38781</v>
+      </c>
+      <c r="N5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
-        <v>46204</v>
+        <v>46224</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F6">
-        <v>51.89</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.48</v>
+        <v>20</v>
+      </c>
+      <c r="G6" t="s">
+        <v>39</v>
       </c>
       <c r="H6">
-        <v>76.8</v>
+        <v>1.65</v>
       </c>
       <c r="I6" s="1">
-        <v>1.51</v>
+        <v>33</v>
       </c>
       <c r="J6">
-        <v>78.34999999999999</v>
-      </c>
-      <c r="K6" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6">
-        <v>38450</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+        <v>1.68</v>
+      </c>
+      <c r="K6" s="1">
+        <v>33.6</v>
+      </c>
+      <c r="L6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6">
+        <v>75529</v>
+      </c>
+      <c r="N6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
-        <v>46210</v>
+        <v>46225</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7">
+        <v>63</v>
+      </c>
+      <c r="G7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7">
+        <v>1.66</v>
+      </c>
+      <c r="I7" s="1">
+        <v>104.58</v>
+      </c>
+      <c r="J7">
+        <v>1.69</v>
+      </c>
+      <c r="K7" s="1">
+        <v>106.47</v>
+      </c>
+      <c r="L7" t="s">
+        <v>44</v>
+      </c>
+      <c r="M7">
+        <v>61200</v>
+      </c>
+      <c r="N7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8">
+        <v>41.94</v>
+      </c>
+      <c r="G8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8">
+        <v>1.67</v>
+      </c>
+      <c r="I8" s="1">
+        <v>70.04000000000001</v>
+      </c>
+      <c r="J8">
+        <v>1.7</v>
+      </c>
+      <c r="K8" s="1">
+        <v>71.3</v>
+      </c>
+      <c r="L8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M8">
+        <v>56698</v>
+      </c>
+      <c r="N8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="3">
+        <v>46226</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9">
+        <v>51.76</v>
+      </c>
+      <c r="G9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9">
+        <v>1.67</v>
+      </c>
+      <c r="I9" s="1">
+        <v>86.44</v>
+      </c>
+      <c r="J9">
+        <v>1.7</v>
+      </c>
+      <c r="K9" s="1">
+        <v>87.98999999999999</v>
+      </c>
+      <c r="L9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M9">
+        <v>55494</v>
+      </c>
+      <c r="N9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="3">
+        <v>46226</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
         <v>20</v>
       </c>
-      <c r="D7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7">
-        <v>52.99</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="H7">
-        <v>78.95999999999999</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="J7">
-        <v>80.54000000000001</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" t="s">
         <v>37</v>
       </c>
-      <c r="L7">
-        <v>74894</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="3">
-        <v>46210</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8">
-        <v>66.92</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="H8">
-        <v>99.70999999999999</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="J8">
-        <v>101.72</v>
-      </c>
-      <c r="K8" t="s">
-        <v>38</v>
-      </c>
-      <c r="L8">
-        <v>6690</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="3">
-        <v>46211</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9">
-        <v>46.83</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="H9">
-        <v>70.23999999999999</v>
-      </c>
-      <c r="I9" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="J9">
-        <v>71.65000000000001</v>
-      </c>
-      <c r="K9" t="s">
+      <c r="F10">
+        <v>65.01000000000001</v>
+      </c>
+      <c r="G10" t="s">
         <v>39</v>
       </c>
-      <c r="L9">
-        <v>56066</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="3">
-        <v>46212</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10">
-        <v>70.29000000000001</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1.49</v>
-      </c>
       <c r="H10">
-        <v>104.73</v>
+        <v>1.67</v>
       </c>
       <c r="I10" s="1">
-        <v>1.52</v>
+        <v>108.57</v>
       </c>
       <c r="J10">
-        <v>106.84</v>
-      </c>
-      <c r="K10" t="s">
-        <v>40</v>
-      </c>
-      <c r="L10">
-        <v>78550</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+        <v>1.7</v>
+      </c>
+      <c r="K10" s="1">
+        <v>110.52</v>
+      </c>
+      <c r="L10" t="s">
+        <v>47</v>
+      </c>
+      <c r="M10">
+        <v>79556</v>
+      </c>
+      <c r="N10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
-        <v>46216</v>
+        <v>46226</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F11">
-        <v>30</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1.53</v>
+        <v>68.04000000000001</v>
+      </c>
+      <c r="G11" t="s">
+        <v>39</v>
       </c>
       <c r="H11">
-        <v>45.9</v>
+        <v>1.67</v>
       </c>
       <c r="I11" s="1">
-        <v>1.56</v>
+        <v>113.63</v>
       </c>
       <c r="J11">
-        <v>46.8</v>
-      </c>
-      <c r="K11" t="s">
-        <v>41</v>
-      </c>
-      <c r="L11">
-        <v>78750</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+        <v>1.7</v>
+      </c>
+      <c r="K11" s="1">
+        <v>115.67</v>
+      </c>
+      <c r="L11" t="s">
+        <v>48</v>
+      </c>
+      <c r="M11">
+        <v>75717</v>
+      </c>
+      <c r="N11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
-        <v>46216</v>
+        <v>46230</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
       </c>
       <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12">
+        <v>40</v>
+      </c>
+      <c r="G12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12">
+        <v>1.72</v>
+      </c>
+      <c r="I12" s="1">
+        <v>68.8</v>
+      </c>
+      <c r="J12">
+        <v>1.75</v>
+      </c>
+      <c r="K12" s="1">
+        <v>70</v>
+      </c>
+      <c r="L12" t="s">
+        <v>49</v>
+      </c>
+      <c r="M12">
+        <v>67770</v>
+      </c>
+      <c r="N12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B13" t="s">
         <v>18</v>
       </c>
-      <c r="D12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12">
-        <v>54.45</v>
-      </c>
-      <c r="G12" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H12">
-        <v>83.31</v>
-      </c>
-      <c r="I12" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J12">
-        <v>84.94</v>
-      </c>
-      <c r="K12" t="s">
-        <v>42</v>
-      </c>
-      <c r="L12">
-        <v>555114</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="3">
-        <v>46218</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13">
+        <v>39.03</v>
+      </c>
+      <c r="G13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13">
+        <v>1.73</v>
+      </c>
+      <c r="I13" s="1">
+        <v>67.52</v>
+      </c>
+      <c r="J13">
+        <v>1.76</v>
+      </c>
+      <c r="K13" s="1">
+        <v>68.69</v>
+      </c>
+      <c r="L13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13">
+        <v>57005</v>
+      </c>
+      <c r="N13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="3">
+        <v>46233</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14">
+        <v>50.15</v>
+      </c>
+      <c r="G14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14">
+        <v>1.73</v>
+      </c>
+      <c r="I14" s="1">
+        <v>86.76000000000001</v>
+      </c>
+      <c r="J14">
+        <v>1.76</v>
+      </c>
+      <c r="K14" s="1">
+        <v>88.26000000000001</v>
+      </c>
+      <c r="L14" t="s">
+        <v>51</v>
+      </c>
+      <c r="M14">
+        <v>8095</v>
+      </c>
+      <c r="N14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B15" t="s">
         <v>14</v>
       </c>
-      <c r="C13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" t="s">
         <v>30</v>
       </c>
-      <c r="E13" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13">
-        <v>40.99</v>
-      </c>
-      <c r="G13" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="H13">
-        <v>63.94</v>
-      </c>
-      <c r="I13" s="1">
-        <v>1.59</v>
-      </c>
-      <c r="J13">
-        <v>65.17</v>
-      </c>
-      <c r="K13" t="s">
-        <v>43</v>
-      </c>
-      <c r="L13">
-        <v>56390</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>9</v>
+      <c r="E15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15">
+        <v>34.13</v>
+      </c>
+      <c r="G15" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15">
+        <v>1.52</v>
+      </c>
+      <c r="I15" s="1">
+        <v>51.88</v>
+      </c>
+      <c r="J15">
+        <v>1.55</v>
+      </c>
+      <c r="K15" s="1">
+        <v>52.9</v>
+      </c>
+      <c r="L15" t="s">
+        <v>52</v>
+      </c>
+      <c r="M15">
+        <v>154856</v>
+      </c>
+      <c r="N15" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="7">
-        <v>618.2</v>
-      </c>
-      <c r="C18" s="7">
+      <c r="A18" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="7">
+        <v>611.9400000000001</v>
+      </c>
+      <c r="C20" s="7">
         <v>12</v>
       </c>
-      <c r="D18" s="8">
-        <v>1.4967</v>
-      </c>
-      <c r="E18" s="7">
-        <v>925.27</v>
-      </c>
-      <c r="F18" s="7">
-        <v>943.8099999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="10">
-        <v>618.2</v>
-      </c>
-      <c r="C19" s="10">
-        <v>12</v>
-      </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="10">
-        <v>925.27</v>
-      </c>
-      <c r="F19" s="10">
-        <v>943.8099999999999</v>
+      <c r="D20" s="8">
+        <v>1.6608</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1016.31</v>
+      </c>
+      <c r="F20" s="7">
+        <v>1034.65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="7">
+        <v>73.3</v>
+      </c>
+      <c r="C21" s="7">
+        <v>2</v>
+      </c>
+      <c r="D21" s="8">
+        <v>1.4986</v>
+      </c>
+      <c r="E21" s="7">
+        <v>109.85</v>
+      </c>
+      <c r="F21" s="7">
+        <v>112.05</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="10">
+        <v>685.24</v>
+      </c>
+      <c r="C22" s="10">
+        <v>14</v>
+      </c>
+      <c r="D22" s="8"/>
+      <c r="E22" s="10">
+        <v>1126.16</v>
+      </c>
+      <c r="F22" s="10">
+        <v>1146.7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
@@ -242,7 +242,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1374,7 +1374,7 @@
         <v>2</v>
       </c>
       <c r="D21" s="8">
-        <v>1.4986</v>
+        <v>1.498636</v>
       </c>
       <c r="E21" s="7">
         <v>109.85</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="74">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -634,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -647,13 +650,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -696,626 +699,671 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2">
         <v>56</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H2">
+        <v>1.499</v>
+      </c>
+      <c r="I2" s="1">
         <v>1.58</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>88.48</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>1.61</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>90.16</v>
       </c>
-      <c r="L2" t="s">
-        <v>40</v>
-      </c>
-      <c r="M2">
+      <c r="M2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2">
         <v>31596</v>
       </c>
-      <c r="N2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46219</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F3">
-        <v>65.40000000000001</v>
+        <v>65.398</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H3">
+        <v>1.499</v>
+      </c>
+      <c r="I3" s="1">
         <v>1.58</v>
       </c>
-      <c r="I3" s="1">
-        <v>103.33</v>
-      </c>
       <c r="J3">
+        <v>103.32884</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.61</v>
       </c>
-      <c r="K3" s="1">
-        <v>105.29</v>
-      </c>
-      <c r="L3" t="s">
-        <v>41</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>105.29078</v>
+      </c>
+      <c r="M3" t="s">
+        <v>42</v>
+      </c>
+      <c r="N3">
         <v>79080</v>
       </c>
-      <c r="N3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46220</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F4">
-        <v>39.17</v>
+        <v>39.172</v>
       </c>
       <c r="G4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H4">
+        <v>1.369</v>
+      </c>
+      <c r="I4" s="1">
         <v>1.48</v>
       </c>
-      <c r="I4" s="1">
-        <v>57.97</v>
-      </c>
       <c r="J4">
+        <v>57.97456</v>
+      </c>
+      <c r="K4" s="1">
         <v>1.51</v>
       </c>
-      <c r="K4" s="1">
-        <v>59.15</v>
-      </c>
-      <c r="L4" t="s">
-        <v>42</v>
-      </c>
-      <c r="M4">
+      <c r="L4" s="1">
+        <v>59.14972</v>
+      </c>
+      <c r="M4" t="s">
+        <v>43</v>
+      </c>
+      <c r="N4">
         <v>145632</v>
       </c>
-      <c r="N4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="3">
         <v>46223</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5">
-        <v>51.61</v>
+        <v>51.607</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H5">
+        <v>1.546</v>
+      </c>
+      <c r="I5" s="1">
         <v>1.65</v>
       </c>
-      <c r="I5" s="1">
-        <v>85.16</v>
-      </c>
       <c r="J5">
+        <v>85.15155</v>
+      </c>
+      <c r="K5" s="1">
         <v>1.68</v>
       </c>
-      <c r="K5" s="1">
-        <v>86.7</v>
-      </c>
-      <c r="L5" t="s">
-        <v>43</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="1">
+        <v>86.69976</v>
+      </c>
+      <c r="M5" t="s">
+        <v>44</v>
+      </c>
+      <c r="N5">
         <v>38781</v>
       </c>
-      <c r="N5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="3">
         <v>46224</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6">
         <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H6">
+        <v>1.564</v>
+      </c>
+      <c r="I6" s="1">
         <v>1.65</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>33</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>1.68</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>33.6</v>
       </c>
-      <c r="L6" t="s">
-        <v>44</v>
-      </c>
-      <c r="M6">
+      <c r="M6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6">
         <v>75529</v>
       </c>
-      <c r="N6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="3">
         <v>46225</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7">
         <v>63</v>
       </c>
       <c r="G7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H7">
+        <v>1.588</v>
+      </c>
+      <c r="I7" s="1">
         <v>1.66</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>104.58</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>1.69</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>106.47</v>
       </c>
-      <c r="L7" t="s">
-        <v>44</v>
-      </c>
-      <c r="M7">
+      <c r="M7" t="s">
+        <v>45</v>
+      </c>
+      <c r="N7">
         <v>61200</v>
       </c>
-      <c r="N7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="3">
         <v>46225</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F8">
-        <v>41.94</v>
+        <v>41.941</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H8">
+        <v>1.588</v>
+      </c>
+      <c r="I8" s="1">
         <v>1.67</v>
       </c>
-      <c r="I8" s="1">
-        <v>70.04000000000001</v>
-      </c>
       <c r="J8">
+        <v>70.04147</v>
+      </c>
+      <c r="K8" s="1">
         <v>1.7</v>
       </c>
-      <c r="K8" s="1">
-        <v>71.3</v>
-      </c>
-      <c r="L8" t="s">
-        <v>45</v>
-      </c>
-      <c r="M8">
+      <c r="L8" s="1">
+        <v>71.2997</v>
+      </c>
+      <c r="M8" t="s">
+        <v>46</v>
+      </c>
+      <c r="N8">
         <v>56698</v>
       </c>
-      <c r="N8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="3">
         <v>46226</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F9">
-        <v>51.76</v>
+        <v>51.759</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H9">
+        <v>1.588</v>
+      </c>
+      <c r="I9" s="1">
         <v>1.67</v>
       </c>
-      <c r="I9" s="1">
-        <v>86.44</v>
-      </c>
       <c r="J9">
+        <v>86.43753</v>
+      </c>
+      <c r="K9" s="1">
         <v>1.7</v>
       </c>
-      <c r="K9" s="1">
-        <v>87.98999999999999</v>
-      </c>
-      <c r="L9" t="s">
-        <v>46</v>
-      </c>
-      <c r="M9">
+      <c r="L9" s="1">
+        <v>87.9903</v>
+      </c>
+      <c r="M9" t="s">
+        <v>47</v>
+      </c>
+      <c r="N9">
         <v>55494</v>
       </c>
-      <c r="N9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="3">
         <v>46226</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F10">
-        <v>65.01000000000001</v>
+        <v>65.012</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H10">
+        <v>1.588</v>
+      </c>
+      <c r="I10" s="1">
         <v>1.67</v>
       </c>
-      <c r="I10" s="1">
-        <v>108.57</v>
-      </c>
       <c r="J10">
+        <v>108.57004</v>
+      </c>
+      <c r="K10" s="1">
         <v>1.7</v>
       </c>
-      <c r="K10" s="1">
-        <v>110.52</v>
-      </c>
-      <c r="L10" t="s">
-        <v>47</v>
-      </c>
-      <c r="M10">
+      <c r="L10" s="1">
+        <v>110.5204</v>
+      </c>
+      <c r="M10" t="s">
+        <v>48</v>
+      </c>
+      <c r="N10">
         <v>79556</v>
       </c>
-      <c r="N10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="3">
         <v>46226</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11">
-        <v>68.04000000000001</v>
+        <v>68.041</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H11">
+        <v>1.588</v>
+      </c>
+      <c r="I11" s="1">
         <v>1.67</v>
       </c>
-      <c r="I11" s="1">
-        <v>113.63</v>
-      </c>
       <c r="J11">
+        <v>113.62847</v>
+      </c>
+      <c r="K11" s="1">
         <v>1.7</v>
       </c>
-      <c r="K11" s="1">
-        <v>115.67</v>
-      </c>
-      <c r="L11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11">
+      <c r="L11" s="1">
+        <v>115.6697</v>
+      </c>
+      <c r="M11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N11">
         <v>75717</v>
       </c>
-      <c r="N11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="3">
         <v>46230</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F12">
         <v>40</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H12">
+        <v>1.619</v>
+      </c>
+      <c r="I12" s="1">
         <v>1.72</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>68.8</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>1.75</v>
       </c>
-      <c r="K12" s="1">
+      <c r="L12" s="1">
         <v>70</v>
       </c>
-      <c r="L12" t="s">
-        <v>49</v>
-      </c>
-      <c r="M12">
+      <c r="M12" t="s">
+        <v>50</v>
+      </c>
+      <c r="N12">
         <v>67770</v>
       </c>
-      <c r="N12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="3">
         <v>46232</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13">
-        <v>39.03</v>
+        <v>39.028</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H13">
+        <v>1.674</v>
+      </c>
+      <c r="I13" s="1">
         <v>1.73</v>
       </c>
-      <c r="I13" s="1">
-        <v>67.52</v>
-      </c>
       <c r="J13">
+        <v>67.51844</v>
+      </c>
+      <c r="K13" s="1">
         <v>1.76</v>
       </c>
-      <c r="K13" s="1">
-        <v>68.69</v>
-      </c>
-      <c r="L13" t="s">
-        <v>50</v>
-      </c>
-      <c r="M13">
+      <c r="L13" s="1">
+        <v>68.68928</v>
+      </c>
+      <c r="M13" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13">
         <v>57005</v>
       </c>
-      <c r="N13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="3">
         <v>46233</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F14">
-        <v>50.15</v>
+        <v>50.148</v>
       </c>
       <c r="G14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H14">
+        <v>1.674</v>
+      </c>
+      <c r="I14" s="1">
         <v>1.73</v>
       </c>
-      <c r="I14" s="1">
-        <v>86.76000000000001</v>
-      </c>
       <c r="J14">
+        <v>86.75604</v>
+      </c>
+      <c r="K14" s="1">
         <v>1.76</v>
       </c>
-      <c r="K14" s="1">
-        <v>88.26000000000001</v>
-      </c>
-      <c r="L14" t="s">
-        <v>51</v>
-      </c>
-      <c r="M14">
+      <c r="L14" s="1">
+        <v>88.26048</v>
+      </c>
+      <c r="M14" t="s">
+        <v>52</v>
+      </c>
+      <c r="N14">
         <v>8095</v>
       </c>
-      <c r="N14" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="3">
         <v>46234</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F15">
-        <v>34.13</v>
+        <v>34.129</v>
       </c>
       <c r="G15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H15">
+        <v>1.459</v>
+      </c>
+      <c r="I15" s="1">
         <v>1.52</v>
       </c>
-      <c r="I15" s="1">
-        <v>51.88</v>
-      </c>
       <c r="J15">
+        <v>51.87608</v>
+      </c>
+      <c r="K15" s="1">
         <v>1.55</v>
       </c>
-      <c r="K15" s="1">
-        <v>52.9</v>
-      </c>
-      <c r="L15" t="s">
-        <v>52</v>
-      </c>
-      <c r="M15">
+      <c r="L15" s="1">
+        <v>52.89995</v>
+      </c>
+      <c r="M15" t="s">
+        <v>53</v>
+      </c>
+      <c r="N15">
         <v>154856</v>
       </c>
-      <c r="N15" t="s">
-        <v>66</v>
+      <c r="O15" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -1325,39 +1373,39 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20" s="7">
-        <v>611.9400000000001</v>
+        <v>611.934</v>
       </c>
       <c r="C20" s="7">
         <v>12</v>
       </c>
       <c r="D20" s="8">
-        <v>1.6608</v>
+        <v>1.660788</v>
       </c>
       <c r="E20" s="7">
-        <v>1016.31</v>
+        <v>1016.29</v>
       </c>
       <c r="F20" s="7">
         <v>1034.65</v>
@@ -1365,16 +1413,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" s="7">
-        <v>73.3</v>
+        <v>73.301</v>
       </c>
       <c r="C21" s="7">
         <v>2</v>
       </c>
       <c r="D21" s="8">
-        <v>1.498636</v>
+        <v>1.498624</v>
       </c>
       <c r="E21" s="7">
         <v>109.85</v>
@@ -1385,17 +1433,17 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B22" s="10">
-        <v>685.24</v>
+        <v>685.235</v>
       </c>
       <c r="C22" s="10">
         <v>14</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="10">
-        <v>1126.16</v>
+        <v>1126.14</v>
       </c>
       <c r="F22" s="10">
         <v>1146.7</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="73">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -243,9 +240,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -339,10 +336,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -637,7 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -650,13 +647,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -699,671 +696,626 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2">
         <v>56</v>
       </c>
       <c r="G2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2">
+        <v>1.58</v>
+      </c>
+      <c r="I2" s="1">
+        <v>88.48</v>
+      </c>
+      <c r="J2">
+        <v>1.61</v>
+      </c>
+      <c r="K2" s="1">
+        <v>90.16</v>
+      </c>
+      <c r="L2" t="s">
         <v>40</v>
       </c>
-      <c r="H2">
-        <v>1.499</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="J2">
-        <v>88.48</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L2" s="1">
-        <v>90.16</v>
-      </c>
-      <c r="M2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>31596</v>
       </c>
-      <c r="O2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46219</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3">
         <v>65.398</v>
       </c>
       <c r="G3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H3">
-        <v>1.499</v>
+        <v>1.58</v>
       </c>
       <c r="I3" s="1">
-        <v>1.58</v>
+        <v>103.329</v>
       </c>
       <c r="J3">
-        <v>103.32884</v>
+        <v>1.61</v>
       </c>
       <c r="K3" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L3" s="1">
-        <v>105.29078</v>
-      </c>
-      <c r="M3" t="s">
-        <v>42</v>
-      </c>
-      <c r="N3">
+        <v>105.291</v>
+      </c>
+      <c r="L3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3">
         <v>79080</v>
       </c>
-      <c r="O3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46220</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4">
         <v>39.172</v>
       </c>
       <c r="G4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H4">
-        <v>1.369</v>
+        <v>1.48</v>
       </c>
       <c r="I4" s="1">
-        <v>1.48</v>
+        <v>57.975</v>
       </c>
       <c r="J4">
-        <v>57.97456</v>
+        <v>1.51</v>
       </c>
       <c r="K4" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L4" s="1">
-        <v>59.14972</v>
-      </c>
-      <c r="M4" t="s">
-        <v>43</v>
-      </c>
-      <c r="N4">
+        <v>59.15</v>
+      </c>
+      <c r="L4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M4">
         <v>145632</v>
       </c>
-      <c r="O4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46223</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F5">
         <v>51.607</v>
       </c>
       <c r="G5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H5">
-        <v>1.546</v>
+        <v>1.65</v>
       </c>
       <c r="I5" s="1">
-        <v>1.65</v>
+        <v>85.152</v>
       </c>
       <c r="J5">
-        <v>85.15155</v>
+        <v>1.68</v>
       </c>
       <c r="K5" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L5" s="1">
-        <v>86.69976</v>
-      </c>
-      <c r="M5" t="s">
-        <v>44</v>
-      </c>
-      <c r="N5">
+        <v>86.7</v>
+      </c>
+      <c r="L5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5">
         <v>38781</v>
       </c>
-      <c r="O5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46224</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F6">
         <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H6">
-        <v>1.564</v>
+        <v>1.65</v>
       </c>
       <c r="I6" s="1">
-        <v>1.65</v>
+        <v>33</v>
       </c>
       <c r="J6">
-        <v>33</v>
+        <v>1.68</v>
       </c>
       <c r="K6" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L6" s="1">
         <v>33.6</v>
       </c>
-      <c r="M6" t="s">
-        <v>45</v>
-      </c>
-      <c r="N6">
+      <c r="L6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6">
         <v>75529</v>
       </c>
-      <c r="O6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46225</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7">
         <v>63</v>
       </c>
       <c r="G7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H7">
-        <v>1.588</v>
+        <v>1.66</v>
       </c>
       <c r="I7" s="1">
-        <v>1.66</v>
+        <v>104.58</v>
       </c>
       <c r="J7">
-        <v>104.58</v>
+        <v>1.69</v>
       </c>
       <c r="K7" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L7" s="1">
         <v>106.47</v>
       </c>
-      <c r="M7" t="s">
-        <v>45</v>
-      </c>
-      <c r="N7">
+      <c r="L7" t="s">
+        <v>44</v>
+      </c>
+      <c r="M7">
         <v>61200</v>
       </c>
-      <c r="O7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46225</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F8">
         <v>41.941</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H8">
-        <v>1.588</v>
+        <v>1.67</v>
       </c>
       <c r="I8" s="1">
-        <v>1.67</v>
+        <v>70.041</v>
       </c>
       <c r="J8">
-        <v>70.04147</v>
+        <v>1.7</v>
       </c>
       <c r="K8" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L8" s="1">
-        <v>71.2997</v>
-      </c>
-      <c r="M8" t="s">
-        <v>46</v>
-      </c>
-      <c r="N8">
+        <v>71.3</v>
+      </c>
+      <c r="L8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M8">
         <v>56698</v>
       </c>
-      <c r="O8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>46226</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F9">
         <v>51.759</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H9">
-        <v>1.588</v>
+        <v>1.67</v>
       </c>
       <c r="I9" s="1">
-        <v>1.67</v>
+        <v>86.438</v>
       </c>
       <c r="J9">
-        <v>86.43753</v>
+        <v>1.7</v>
       </c>
       <c r="K9" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L9" s="1">
-        <v>87.9903</v>
-      </c>
-      <c r="M9" t="s">
-        <v>47</v>
-      </c>
-      <c r="N9">
+        <v>87.98999999999999</v>
+      </c>
+      <c r="L9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M9">
         <v>55494</v>
       </c>
-      <c r="O9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>46226</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F10">
         <v>65.012</v>
       </c>
       <c r="G10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H10">
-        <v>1.588</v>
+        <v>1.67</v>
       </c>
       <c r="I10" s="1">
-        <v>1.67</v>
+        <v>108.57</v>
       </c>
       <c r="J10">
-        <v>108.57004</v>
+        <v>1.7</v>
       </c>
       <c r="K10" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L10" s="1">
-        <v>110.5204</v>
-      </c>
-      <c r="M10" t="s">
-        <v>48</v>
-      </c>
-      <c r="N10">
+        <v>110.52</v>
+      </c>
+      <c r="L10" t="s">
+        <v>47</v>
+      </c>
+      <c r="M10">
         <v>79556</v>
       </c>
-      <c r="O10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="N10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
         <v>46226</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F11">
         <v>68.041</v>
       </c>
       <c r="G11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H11">
-        <v>1.588</v>
+        <v>1.67</v>
       </c>
       <c r="I11" s="1">
-        <v>1.67</v>
+        <v>113.628</v>
       </c>
       <c r="J11">
-        <v>113.62847</v>
+        <v>1.7</v>
       </c>
       <c r="K11" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L11" s="1">
-        <v>115.6697</v>
-      </c>
-      <c r="M11" t="s">
-        <v>49</v>
-      </c>
-      <c r="N11">
+        <v>115.67</v>
+      </c>
+      <c r="L11" t="s">
+        <v>48</v>
+      </c>
+      <c r="M11">
         <v>75717</v>
       </c>
-      <c r="O11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="N11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
         <v>46230</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" t="s">
         <v>37</v>
-      </c>
-      <c r="E12" t="s">
-        <v>38</v>
       </c>
       <c r="F12">
         <v>40</v>
       </c>
       <c r="G12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H12">
-        <v>1.619</v>
+        <v>1.72</v>
       </c>
       <c r="I12" s="1">
-        <v>1.72</v>
+        <v>68.8</v>
       </c>
       <c r="J12">
-        <v>68.8</v>
+        <v>1.75</v>
       </c>
       <c r="K12" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L12" s="1">
         <v>70</v>
       </c>
-      <c r="M12" t="s">
-        <v>50</v>
-      </c>
-      <c r="N12">
+      <c r="L12" t="s">
+        <v>49</v>
+      </c>
+      <c r="M12">
         <v>67770</v>
       </c>
-      <c r="O12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="N12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="3">
         <v>46232</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F13">
         <v>39.028</v>
       </c>
       <c r="G13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H13">
-        <v>1.674</v>
+        <v>1.73</v>
       </c>
       <c r="I13" s="1">
-        <v>1.73</v>
+        <v>67.518</v>
       </c>
       <c r="J13">
-        <v>67.51844</v>
+        <v>1.76</v>
       </c>
       <c r="K13" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L13" s="1">
-        <v>68.68928</v>
-      </c>
-      <c r="M13" t="s">
-        <v>51</v>
-      </c>
-      <c r="N13">
+        <v>68.68899999999999</v>
+      </c>
+      <c r="L13" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13">
         <v>57005</v>
       </c>
-      <c r="O13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="N13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="3">
         <v>46233</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F14">
         <v>50.148</v>
       </c>
       <c r="G14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H14">
-        <v>1.674</v>
+        <v>1.73</v>
       </c>
       <c r="I14" s="1">
-        <v>1.73</v>
+        <v>86.756</v>
       </c>
       <c r="J14">
-        <v>86.75604</v>
+        <v>1.76</v>
       </c>
       <c r="K14" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L14" s="1">
-        <v>88.26048</v>
-      </c>
-      <c r="M14" t="s">
-        <v>52</v>
-      </c>
-      <c r="N14">
+        <v>88.26000000000001</v>
+      </c>
+      <c r="L14" t="s">
+        <v>51</v>
+      </c>
+      <c r="M14">
         <v>8095</v>
       </c>
-      <c r="O14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="N14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="3">
         <v>46234</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F15">
         <v>34.129</v>
       </c>
       <c r="G15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H15">
-        <v>1.459</v>
+        <v>1.52</v>
       </c>
       <c r="I15" s="1">
-        <v>1.52</v>
+        <v>51.876</v>
       </c>
       <c r="J15">
-        <v>51.87608</v>
+        <v>1.55</v>
       </c>
       <c r="K15" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L15" s="1">
-        <v>52.89995</v>
-      </c>
-      <c r="M15" t="s">
-        <v>53</v>
-      </c>
-      <c r="N15">
+        <v>52.9</v>
+      </c>
+      <c r="L15" t="s">
+        <v>52</v>
+      </c>
+      <c r="M15">
         <v>154856</v>
       </c>
-      <c r="O15" t="s">
-        <v>67</v>
+      <c r="N15" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -1373,67 +1325,67 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>72</v>
-      </c>
       <c r="E19" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" s="7">
         <v>611.934</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="8">
         <v>12</v>
       </c>
       <c r="D20" s="8">
-        <v>1.660788</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1016.29</v>
-      </c>
-      <c r="F20" s="7">
+        <v>1.661</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1016.292</v>
+      </c>
+      <c r="F20" s="8">
         <v>1034.65</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B21" s="7">
         <v>73.301</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="8">
         <v>2</v>
       </c>
       <c r="D21" s="8">
-        <v>1.498624</v>
-      </c>
-      <c r="E21" s="7">
-        <v>109.85</v>
-      </c>
-      <c r="F21" s="7">
+        <v>1.499</v>
+      </c>
+      <c r="E21" s="8">
+        <v>109.851</v>
+      </c>
+      <c r="F21" s="8">
         <v>112.05</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B22" s="10">
         <v>685.235</v>
@@ -1443,7 +1395,7 @@
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="10">
-        <v>1126.14</v>
+        <v>1126.143</v>
       </c>
       <c r="F22" s="10">
         <v>1146.7</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="69">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -55,115 +58,151 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>Варна Цар Освободител</t>
-  </si>
-  <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна Евkсиноград</t>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>B6386HH</t>
+  </si>
+  <si>
+    <t>B7846TP</t>
+  </si>
+  <si>
+    <t>B4160TK</t>
+  </si>
+  <si>
+    <t>B8917BP</t>
+  </si>
+  <si>
+    <t>B0452TC</t>
+  </si>
+  <si>
+    <t>B2207PP</t>
   </si>
   <si>
     <t>B4161TK</t>
   </si>
   <si>
-    <t>B5383XE</t>
-  </si>
-  <si>
-    <t>B7846TP</t>
-  </si>
-  <si>
-    <t>B8917BP</t>
-  </si>
-  <si>
-    <t>B6386HH</t>
-  </si>
-  <si>
-    <t>B4160TK</t>
+    <t>B5379XE</t>
   </si>
   <si>
     <t>B7845TP</t>
   </si>
   <si>
-    <t>B5379XE</t>
-  </si>
-  <si>
-    <t>B0452TC</t>
+    <t>78970155027721301</t>
+  </si>
+  <si>
+    <t>78970155027721194</t>
+  </si>
+  <si>
+    <t>78970155027721293</t>
+  </si>
+  <si>
+    <t>78970155027721269</t>
+  </si>
+  <si>
+    <t>78970155027721202</t>
+  </si>
+  <si>
+    <t>78970155027721178</t>
   </si>
   <si>
     <t>78970155027721285</t>
   </si>
   <si>
-    <t>78970155027721236</t>
-  </si>
-  <si>
-    <t>78970155027721194</t>
-  </si>
-  <si>
-    <t>78970155027721269</t>
-  </si>
-  <si>
-    <t>78970155027721301</t>
-  </si>
-  <si>
-    <t>78970155027721293</t>
+    <t>78970155027721244</t>
   </si>
   <si>
     <t>78970155027721251</t>
   </si>
   <si>
-    <t>78970155027721244</t>
-  </si>
-  <si>
-    <t>78970155027721202</t>
-  </si>
-  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>13:41</t>
-  </si>
-  <si>
-    <t>13:43</t>
-  </si>
-  <si>
-    <t>13:56</t>
-  </si>
-  <si>
-    <t>10:18</t>
-  </si>
-  <si>
-    <t>10:06</t>
-  </si>
-  <si>
-    <t>12:37</t>
-  </si>
-  <si>
-    <t>10:54</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>13:19</t>
-  </si>
-  <si>
-    <t>13:33</t>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>10:29:00</t>
+  </si>
+  <si>
+    <t>13:33:00</t>
+  </si>
+  <si>
+    <t>13:31:00</t>
+  </si>
+  <si>
+    <t>13:40:00</t>
+  </si>
+  <si>
+    <t>10:13:00</t>
+  </si>
+  <si>
+    <t>13:23:00</t>
+  </si>
+  <si>
+    <t>14:11:00</t>
+  </si>
+  <si>
+    <t>13:52:00</t>
+  </si>
+  <si>
+    <t>13:29:00</t>
+  </si>
+  <si>
+    <t>13:07:00</t>
+  </si>
+  <si>
+    <t>12:33:00</t>
+  </si>
+  <si>
+    <t>10:49:00</t>
+  </si>
+  <si>
+    <t>3236508147 3236508147</t>
+  </si>
+  <si>
+    <t>3236559755 3236559755</t>
+  </si>
+  <si>
+    <t>3236606812 3236606812</t>
+  </si>
+  <si>
+    <t>3236660105 3236660105</t>
+  </si>
+  <si>
+    <t>3236661468 3236661468</t>
+  </si>
+  <si>
+    <t>3236828268 3236828268</t>
+  </si>
+  <si>
+    <t>3236878929 3236878929</t>
+  </si>
+  <si>
+    <t>3236924571 3236924571</t>
+  </si>
+  <si>
+    <t>3236924950 3236924950</t>
+  </si>
+  <si>
+    <t>3236954992 3236954992</t>
+  </si>
+  <si>
+    <t>3237075098 3237075098</t>
+  </si>
+  <si>
+    <t>3237211433 3237211433</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ</t>
@@ -188,10 +227,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -271,7 +311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -285,10 +325,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -583,7 +625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -592,16 +634,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -641,13 +684,16 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46237</v>
+        <v>46251</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -659,33 +705,36 @@
         <v>36</v>
       </c>
       <c r="F2">
-        <v>57</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="H2">
-        <v>100.32</v>
+        <v>73.44</v>
+      </c>
+      <c r="G2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1.657</v>
       </c>
       <c r="I2" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="J2">
-        <v>102.03</v>
-      </c>
-      <c r="K2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L2">
-        <v>55898</v>
+        <v>121.69</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="K2" s="1">
+        <v>132.192</v>
+      </c>
+      <c r="L2" t="s">
+        <v>39</v>
       </c>
       <c r="M2">
-        <v>289167</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>81063</v>
+      </c>
+      <c r="N2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
-        <v>46237</v>
+        <v>46252</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
@@ -700,36 +749,39 @@
         <v>36</v>
       </c>
       <c r="F3">
-        <v>30</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="H3">
-        <v>52.8</v>
+        <v>56.85</v>
+      </c>
+      <c r="G3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1.677</v>
       </c>
       <c r="I3" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="J3">
-        <v>53.7</v>
-      </c>
-      <c r="K3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L3">
-        <v>7520</v>
+        <v>95.337</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="K3" s="1">
+        <v>102.33</v>
+      </c>
+      <c r="L3" t="s">
+        <v>40</v>
       </c>
       <c r="M3">
-        <v>134139</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>32370</v>
+      </c>
+      <c r="N3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
-        <v>46237</v>
+        <v>46253</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
@@ -741,36 +793,39 @@
         <v>36</v>
       </c>
       <c r="F4">
-        <v>60.989</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="H4">
-        <v>107.341</v>
+        <v>42.05</v>
+      </c>
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1.677</v>
       </c>
       <c r="I4" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="J4">
-        <v>109.17</v>
-      </c>
-      <c r="K4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L4">
-        <v>32005</v>
+        <v>70.518</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1.82</v>
+      </c>
+      <c r="K4" s="1">
+        <v>76.53100000000001</v>
+      </c>
+      <c r="L4" t="s">
+        <v>41</v>
       </c>
       <c r="M4">
-        <v>229284</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>57925</v>
+      </c>
+      <c r="N4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
-        <v>46238</v>
+        <v>46254</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
@@ -784,31 +839,34 @@
       <c r="F5">
         <v>20</v>
       </c>
-      <c r="G5" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="H5">
-        <v>35.4</v>
+      <c r="G5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1.689</v>
       </c>
       <c r="I5" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="J5">
-        <v>36</v>
-      </c>
-      <c r="K5" t="s">
-        <v>40</v>
-      </c>
-      <c r="L5">
-        <v>76600</v>
+        <v>33.78</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="K5" s="1">
+        <v>36.8</v>
+      </c>
+      <c r="L5" t="s">
+        <v>42</v>
       </c>
       <c r="M5">
-        <v>158977</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>76960</v>
+      </c>
+      <c r="N5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
-        <v>46239</v>
+        <v>46254</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
@@ -823,36 +881,39 @@
         <v>36</v>
       </c>
       <c r="F6">
-        <v>61.378</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="H6">
-        <v>108.639</v>
+        <v>50.01</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1.689</v>
       </c>
       <c r="I6" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="J6">
-        <v>110.48</v>
-      </c>
-      <c r="K6" t="s">
-        <v>41</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
+        <v>84.467</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="K6" s="1">
+        <v>92.018</v>
+      </c>
+      <c r="L6" t="s">
+        <v>43</v>
       </c>
       <c r="M6">
-        <v>242427</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>68230</v>
+      </c>
+      <c r="N6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
-        <v>46239</v>
+        <v>46258</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
@@ -861,39 +922,42 @@
         <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>38.761</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="H7">
-        <v>68.607</v>
+        <v>50.66</v>
+      </c>
+      <c r="G7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1.439</v>
       </c>
       <c r="I7" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="J7">
-        <v>69.77</v>
-      </c>
-      <c r="K7" t="s">
-        <v>42</v>
-      </c>
-      <c r="L7">
-        <v>57295</v>
+        <v>72.90000000000001</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="K7" s="1">
+        <v>79.536</v>
+      </c>
+      <c r="L7" t="s">
+        <v>44</v>
       </c>
       <c r="M7">
-        <v>233343</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>155190</v>
+      </c>
+      <c r="N7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
@@ -905,36 +969,39 @@
         <v>36</v>
       </c>
       <c r="F8">
-        <v>48</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="H8">
-        <v>84.95999999999999</v>
+        <v>54.27</v>
+      </c>
+      <c r="G8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1.708</v>
       </c>
       <c r="I8" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="J8">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="K8" t="s">
-        <v>43</v>
-      </c>
-      <c r="L8">
-        <v>39185</v>
+        <v>92.693</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1.85</v>
+      </c>
+      <c r="K8" s="1">
+        <v>100.4</v>
+      </c>
+      <c r="L8" t="s">
+        <v>45</v>
       </c>
       <c r="M8">
-        <v>161545</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>56678</v>
+      </c>
+      <c r="N8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
-        <v>46244</v>
+        <v>46259</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
         <v>25</v>
@@ -946,159 +1013,171 @@
         <v>36</v>
       </c>
       <c r="F9">
-        <v>73</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="H9">
-        <v>129.21</v>
+        <v>50.02</v>
+      </c>
+      <c r="G9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1.719</v>
       </c>
       <c r="I9" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="J9">
-        <v>131.4</v>
-      </c>
-      <c r="K9" t="s">
-        <v>44</v>
-      </c>
-      <c r="L9">
-        <v>7893</v>
+        <v>85.98399999999999</v>
+      </c>
+      <c r="J9" s="1">
+        <v>1.85</v>
+      </c>
+      <c r="K9" s="1">
+        <v>92.53700000000001</v>
+      </c>
+      <c r="L9" t="s">
+        <v>46</v>
       </c>
       <c r="M9">
-        <v>291410</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>8430</v>
+      </c>
+      <c r="N9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
-        <v>46245</v>
+        <v>46259</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E10" t="s">
         <v>36</v>
       </c>
       <c r="F10">
-        <v>69.989</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="H10">
-        <v>123.881</v>
+        <v>30</v>
+      </c>
+      <c r="G10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1.719</v>
       </c>
       <c r="I10" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="J10">
-        <v>125.98</v>
-      </c>
-      <c r="K10" t="s">
-        <v>45</v>
-      </c>
-      <c r="L10">
-        <v>76558</v>
+        <v>51.57</v>
+      </c>
+      <c r="J10" s="1">
+        <v>1.85</v>
+      </c>
+      <c r="K10" s="1">
+        <v>55.5</v>
+      </c>
+      <c r="L10" t="s">
+        <v>47</v>
       </c>
       <c r="M10">
-        <v>291627</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>39497</v>
+      </c>
+      <c r="N10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
-        <v>46246</v>
+        <v>46260</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E11" t="s">
         <v>36</v>
       </c>
       <c r="F11">
-        <v>41.889</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="H11">
-        <v>74.14400000000001</v>
+        <v>38.44</v>
+      </c>
+      <c r="G11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1.719</v>
       </c>
       <c r="I11" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="J11">
-        <v>75.40000000000001</v>
-      </c>
-      <c r="K11" t="s">
-        <v>46</v>
-      </c>
-      <c r="L11">
-        <v>57599</v>
+        <v>66.078</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1.85</v>
+      </c>
+      <c r="K11" s="1">
+        <v>71.114</v>
+      </c>
+      <c r="L11" t="s">
+        <v>48</v>
       </c>
       <c r="M11">
-        <v>140061</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>58220</v>
+      </c>
+      <c r="N11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
-        <v>46246</v>
+        <v>46262</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E12" t="s">
         <v>36</v>
       </c>
       <c r="F12">
-        <v>35</v>
-      </c>
-      <c r="G12" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="H12">
-        <v>61.95</v>
+        <v>68</v>
+      </c>
+      <c r="G12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1.719</v>
       </c>
       <c r="I12" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="J12">
-        <v>63</v>
-      </c>
-      <c r="K12" t="s">
-        <v>47</v>
-      </c>
-      <c r="L12">
-        <v>67895</v>
+        <v>116.892</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1.85</v>
+      </c>
+      <c r="K12" s="1">
+        <v>125.8</v>
+      </c>
+      <c r="L12" t="s">
+        <v>49</v>
       </c>
       <c r="M12">
-        <v>137725</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+        <v>77403</v>
+      </c>
+      <c r="N12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="3">
-        <v>46246</v>
+        <v>46265</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
@@ -1110,142 +1189,124 @@
         <v>36</v>
       </c>
       <c r="F13">
-        <v>48.25</v>
-      </c>
-      <c r="G13" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="H13">
-        <v>85.402</v>
+        <v>40</v>
+      </c>
+      <c r="G13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1.719</v>
       </c>
       <c r="I13" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="J13">
-        <v>86.84999999999999</v>
-      </c>
-      <c r="K13" t="s">
-        <v>48</v>
-      </c>
-      <c r="L13">
-        <v>79365</v>
+        <v>68.76000000000001</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="K13" s="1">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="L13" t="s">
+        <v>50</v>
       </c>
       <c r="M13">
-        <v>291898</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="3">
-        <v>46246</v>
-      </c>
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" t="s">
+        <v>81700</v>
+      </c>
+      <c r="N13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F14">
-        <v>30</v>
-      </c>
-      <c r="G14" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="H14">
-        <v>53.1</v>
-      </c>
-      <c r="I14" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="J14">
-        <v>54</v>
-      </c>
-      <c r="K14" t="s">
-        <v>49</v>
-      </c>
-      <c r="L14">
-        <v>7805</v>
-      </c>
-      <c r="M14">
-        <v>137777</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>9</v>
+      <c r="B18" s="7">
+        <v>523.08</v>
+      </c>
+      <c r="C18" s="8">
+        <v>11</v>
+      </c>
+      <c r="D18" s="9">
+        <v>1.6972</v>
+      </c>
+      <c r="E18" s="7">
+        <v>887.77</v>
+      </c>
+      <c r="F18" s="7">
+        <v>958.8200000000001</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B19" s="7">
-        <v>614.256</v>
-      </c>
-      <c r="C19" s="7">
-        <v>13</v>
-      </c>
-      <c r="D19" s="8">
-        <v>1.76759</v>
+        <v>50.66</v>
+      </c>
+      <c r="C19" s="8">
+        <v>1</v>
+      </c>
+      <c r="D19" s="9">
+        <v>1.43901</v>
       </c>
       <c r="E19" s="7">
-        <v>1085.75</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="F19" s="7">
-        <v>1104.18</v>
+        <v>79.54000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" s="10">
-        <v>614.256</v>
-      </c>
-      <c r="C20" s="10">
-        <v>13</v>
-      </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="10">
-        <v>1085.75</v>
-      </c>
-      <c r="F20" s="10">
-        <v>1104.18</v>
+      <c r="A20" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="11">
+        <v>573.74</v>
+      </c>
+      <c r="C20" s="12">
+        <v>12</v>
+      </c>
+      <c r="D20" s="9"/>
+      <c r="E20" s="11">
+        <v>960.67</v>
+      </c>
+      <c r="F20" s="11">
+        <v>1038.36</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A16:F16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ/ДОМАШЕН СОЦИАЛЕН ПАТРОНАЖ.xlsx
@@ -711,10 +711,10 @@
         <v>38</v>
       </c>
       <c r="H2" s="1">
-        <v>1.657</v>
+        <v>1.77</v>
       </c>
       <c r="I2" s="1">
-        <v>121.69</v>
+        <v>129.989</v>
       </c>
       <c r="J2" s="1">
         <v>1.8</v>
@@ -755,10 +755,10 @@
         <v>38</v>
       </c>
       <c r="H3" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I3" s="1">
-        <v>95.337</v>
+        <v>100.624</v>
       </c>
       <c r="J3" s="1">
         <v>1.8</v>
@@ -799,10 +799,10 @@
         <v>38</v>
       </c>
       <c r="H4" s="1">
-        <v>1.677</v>
+        <v>1.79</v>
       </c>
       <c r="I4" s="1">
-        <v>70.518</v>
+        <v>75.27</v>
       </c>
       <c r="J4" s="1">
         <v>1.82</v>
@@ -843,10 +843,10 @@
         <v>38</v>
       </c>
       <c r="H5" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I5" s="1">
-        <v>33.78</v>
+        <v>36.2</v>
       </c>
       <c r="J5" s="1">
         <v>1.84</v>
@@ -887,10 +887,10 @@
         <v>38</v>
       </c>
       <c r="H6" s="1">
-        <v>1.689</v>
+        <v>1.81</v>
       </c>
       <c r="I6" s="1">
-        <v>84.467</v>
+        <v>90.518</v>
       </c>
       <c r="J6" s="1">
         <v>1.84</v>
@@ -931,10 +931,10 @@
         <v>38</v>
       </c>
       <c r="H7" s="1">
-        <v>1.439</v>
+        <v>1.54</v>
       </c>
       <c r="I7" s="1">
-        <v>72.90000000000001</v>
+        <v>78.01600000000001</v>
       </c>
       <c r="J7" s="1">
         <v>1.57</v>
@@ -975,10 +975,10 @@
         <v>38</v>
       </c>
       <c r="H8" s="1">
-        <v>1.708</v>
+        <v>1.82</v>
       </c>
       <c r="I8" s="1">
-        <v>92.693</v>
+        <v>98.771</v>
       </c>
       <c r="J8" s="1">
         <v>1.85</v>
@@ -1019,10 +1019,10 @@
         <v>38</v>
       </c>
       <c r="H9" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I9" s="1">
-        <v>85.98399999999999</v>
+        <v>91.036</v>
       </c>
       <c r="J9" s="1">
         <v>1.85</v>
@@ -1063,10 +1063,10 @@
         <v>38</v>
       </c>
       <c r="H10" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I10" s="1">
-        <v>51.57</v>
+        <v>54.6</v>
       </c>
       <c r="J10" s="1">
         <v>1.85</v>
@@ -1107,10 +1107,10 @@
         <v>38</v>
       </c>
       <c r="H11" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I11" s="1">
-        <v>66.078</v>
+        <v>69.961</v>
       </c>
       <c r="J11" s="1">
         <v>1.85</v>
@@ -1151,10 +1151,10 @@
         <v>38</v>
       </c>
       <c r="H12" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I12" s="1">
-        <v>116.892</v>
+        <v>123.76</v>
       </c>
       <c r="J12" s="1">
         <v>1.85</v>
@@ -1195,10 +1195,10 @@
         <v>38</v>
       </c>
       <c r="H13" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I13" s="1">
-        <v>68.76000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="J13" s="1">
         <v>1.84</v>
@@ -1257,10 +1257,10 @@
         <v>11</v>
       </c>
       <c r="D18" s="9">
-        <v>1.6972</v>
+        <v>1.80303</v>
       </c>
       <c r="E18" s="7">
-        <v>887.77</v>
+        <v>943.13</v>
       </c>
       <c r="F18" s="7">
         <v>958.8200000000001</v>
@@ -1277,10 +1277,10 @@
         <v>1</v>
       </c>
       <c r="D19" s="9">
-        <v>1.43901</v>
+        <v>1.53999</v>
       </c>
       <c r="E19" s="7">
-        <v>72.90000000000001</v>
+        <v>78.02</v>
       </c>
       <c r="F19" s="7">
         <v>79.54000000000001</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="11">
-        <v>960.67</v>
+        <v>1021.15</v>
       </c>
       <c r="F20" s="11">
         <v>1038.36</v>
